--- a/assets/forms/install-form-template.xlsx
+++ b/assets/forms/install-form-template.xlsx
@@ -261,7 +261,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="15" x14ac:knownFonts="1">
+  <fonts count="17" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -357,6 +357,19 @@
       <name val="Angsana New"/>
       <family val="1"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFC00000"/>
+      <name val="Tahoma"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF404040"/>
+      <name val="Tahoma"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="13">
     <fill>
@@ -917,7 +930,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="144">
+  <cellXfs count="146">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1331,6 +1344,12 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="6" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2150,7 +2169,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:H46"/>
+  <dimension ref="A1:J46"/>
   <sheetFormatPr defaultColWidth="8.625" defaultRowHeight="17.7" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="4.625" style="1" customWidth="1"/>
@@ -2174,7 +2193,7 @@
       <c r="G1" s="61"/>
       <c r="H1" s="61"/>
     </row>
-    <row r="2" spans="1:8" ht="18.350000000000001" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:10" ht="18.350000000000001" x14ac:dyDescent="0.4">
       <c r="A2" s="49" t="s">
         <v>53</v>
       </c>
@@ -2185,8 +2204,13 @@
       <c r="F2" s="50"/>
       <c r="G2" s="50"/>
       <c r="H2" s="51"/>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="J2" s="144" t="inlineStr">
+        <is>
+          <t xml:space="preserve">วิธีเซฟเป็น PDF ให้ได้ครบทุกหน้า (หน้าเอกสาร + หน้ารูปภาพ)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A3" s="62" t="s">
         <v>69</v>
       </c>
@@ -2199,8 +2223,13 @@
       </c>
       <c r="G3" s="67"/>
       <c r="H3" s="68"/>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="J3" s="145" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1. File (แฟ้ม) → Save As (บันทึกเป็น) → เลือกชนิดไฟล์ PDF</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A4" s="69" t="s">
         <v>1</v>
       </c>
@@ -2213,8 +2242,13 @@
       </c>
       <c r="G4" s="74"/>
       <c r="H4" s="75"/>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="J4" s="145" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2. กดปุ่ม Options... (ตัวเลือก...) → เลือก Entire workbook (ทั้งเวิร์กบุ๊ก) → OK</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A5" s="69" t="s">
         <v>30</v>
       </c>
@@ -2227,6 +2261,11 @@
       </c>
       <c r="G5" s="82"/>
       <c r="H5" s="83"/>
+      <c r="J5" s="145" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3. กด Save (บันทึก)  — ข้อความนี้อยู่นอกขอบเขตพิมพ์ ไม่ติดไปใน PDF</t>
+        </is>
+      </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A6" s="119" t="s">
@@ -2992,7 +3031,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{51496EA4-4132-4452-9309-55127D2AD8A7}">
-  <dimension ref="A1:J36"/>
+  <dimension ref="A1:L36"/>
   <sheetFormatPr defaultColWidth="8.625" defaultRowHeight="17.7" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="2.625" style="1" customWidth="1"/>
@@ -3019,7 +3058,7 @@
       <c r="I1" s="135"/>
       <c r="J1" s="136"/>
     </row>
-    <row r="2" spans="1:10" ht="21.1" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:12" ht="21.1" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A2" s="137" t="s">
         <v>0</v>
       </c>
@@ -3038,8 +3077,13 @@
       </c>
       <c r="I2" s="140"/>
       <c r="J2" s="141"/>
-    </row>
-    <row r="3" spans="1:10" ht="18.350000000000001" x14ac:dyDescent="0.4">
+      <c r="L2" s="144" t="inlineStr">
+        <is>
+          <t xml:space="preserve">วิธีเซฟเป็น PDF ให้ได้ครบทุกหน้า (หน้าเอกสาร + หน้ารูปภาพ)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" spans="1:12" ht="18.350000000000001" x14ac:dyDescent="0.4">
       <c r="A3" s="19"/>
       <c r="B3" s="20"/>
       <c r="C3" s="20"/>
@@ -3050,8 +3094,13 @@
       <c r="H3" s="20"/>
       <c r="I3" s="20"/>
       <c r="J3" s="21"/>
-    </row>
-    <row r="4" spans="1:10" ht="18.350000000000001" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="L3" s="145" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1. File (แฟ้ม) → Save As (บันทึกเป็น) → เลือกชนิดไฟล์ PDF</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" spans="1:12" ht="18.350000000000001" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A4" s="19"/>
       <c r="B4" s="127" t="s">
         <v>57</v>
@@ -3067,8 +3116,13 @@
       </c>
       <c r="I4" s="133"/>
       <c r="J4" s="21"/>
-    </row>
-    <row r="5" spans="1:10" ht="18.350000000000001" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="L4" s="145" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2. กดปุ่ม Options... (ตัวเลือก...) → เลือก Entire workbook (ทั้งเวิร์กบุ๊ก) → OK</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" spans="1:12" ht="18.350000000000001" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A5" s="19"/>
       <c r="B5" s="129"/>
       <c r="C5" s="130"/>
@@ -3078,6 +3132,11 @@
       <c r="H5" s="133"/>
       <c r="I5" s="133"/>
       <c r="J5" s="21"/>
+      <c r="L5" s="145" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3. กด Save (บันทึก)  — ข้อความนี้อยู่นอกขอบเขตพิมพ์ ไม่ติดไปใน PDF</t>
+        </is>
+      </c>
     </row>
     <row r="6" spans="1:10" ht="18.350000000000001" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A6" s="19"/>
@@ -3506,7 +3565,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F5845FA4-988D-4571-AC59-F62C504A990F}">
-  <dimension ref="A1:J36"/>
+  <dimension ref="A1:L36"/>
   <sheetFormatPr defaultColWidth="8.625" defaultRowHeight="17.7" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="2.625" style="1" customWidth="1"/>
@@ -3533,7 +3592,7 @@
       <c r="I1" s="135"/>
       <c r="J1" s="136"/>
     </row>
-    <row r="2" spans="1:10" ht="21.1" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:12" ht="21.1" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A2" s="137" t="s">
         <v>0</v>
       </c>
@@ -3552,8 +3611,13 @@
       </c>
       <c r="I2" s="140"/>
       <c r="J2" s="141"/>
-    </row>
-    <row r="3" spans="1:10" ht="18.350000000000001" x14ac:dyDescent="0.4">
+      <c r="L2" s="144" t="inlineStr">
+        <is>
+          <t xml:space="preserve">วิธีเซฟเป็น PDF ให้ได้ครบทุกหน้า (หน้าเอกสาร + หน้ารูปภาพ)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" spans="1:12" ht="18.350000000000001" x14ac:dyDescent="0.4">
       <c r="A3" s="19"/>
       <c r="B3" s="20"/>
       <c r="C3" s="20"/>
@@ -3564,8 +3628,13 @@
       <c r="H3" s="20"/>
       <c r="I3" s="20"/>
       <c r="J3" s="21"/>
-    </row>
-    <row r="4" spans="1:10" ht="18.350000000000001" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="L3" s="145" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1. File (แฟ้ม) → Save As (บันทึกเป็น) → เลือกชนิดไฟล์ PDF</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" spans="1:12" ht="18.350000000000001" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A4" s="19"/>
       <c r="B4" s="127" t="s">
         <v>57</v>
@@ -3581,8 +3650,13 @@
       </c>
       <c r="I4" s="133"/>
       <c r="J4" s="21"/>
-    </row>
-    <row r="5" spans="1:10" ht="18.350000000000001" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="L4" s="145" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2. กดปุ่ม Options... (ตัวเลือก...) → เลือก Entire workbook (ทั้งเวิร์กบุ๊ก) → OK</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" spans="1:12" ht="18.350000000000001" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A5" s="19"/>
       <c r="B5" s="129"/>
       <c r="C5" s="130"/>
@@ -3592,6 +3666,11 @@
       <c r="H5" s="133"/>
       <c r="I5" s="133"/>
       <c r="J5" s="21"/>
+      <c r="L5" s="145" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3. กด Save (บันทึก)  — ข้อความนี้อยู่นอกขอบเขตพิมพ์ ไม่ติดไปใน PDF</t>
+        </is>
+      </c>
     </row>
     <row r="6" spans="1:10" ht="18.350000000000001" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A6" s="19"/>

--- a/assets/forms/install-form-template.xlsx
+++ b/assets/forms/install-form-template.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="Z:\Equipment\Air\เอกสารแบบฟอร์มซ่อม ล้าง\ฟอร์ม 2026\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Project Aircon-manager\assets\forms\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2A60D430-C13A-4E8B-B7F8-DBCF0F8B599C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7B57AEAD-F2A9-4F6F-BD37-DC32895E8BDC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-109" yWindow="-109" windowWidth="26301" windowHeight="14169" tabRatio="500" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="เอกสารติดตั้ง" sheetId="1" r:id="rId1"/>
@@ -18,9 +18,9 @@
     <sheet name="รูปภาพ_เครื่องที่ 2" sheetId="5" r:id="rId3"/>
   </sheets>
   <definedNames>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">เอกสารติดตั้ง!$A$1:$H$46</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="1">'รูปภาพ_เครื่องที่ 1'!$A$1:$J$36</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="2">'รูปภาพ_เครื่องที่ 2'!$A$1:$J$36</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">เอกสารติดตั้ง!$A$1:$H$46</definedName>
   </definedNames>
   <calcPr calcId="191029" iterateDelta="1E-4"/>
   <extLst>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="131" uniqueCount="72">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="143" uniqueCount="76">
   <si>
     <t>Node / รหัส Node</t>
   </si>
@@ -255,6 +255,18 @@
   </si>
   <si>
     <t>รูปก่อนดำเนินการติดตั้ง</t>
+  </si>
+  <si>
+    <t>วิธีเซฟเป็น PDF ให้ได้ครบทุกหน้า (หน้าเอกสาร + หน้ารูปภาพ)</t>
+  </si>
+  <si>
+    <t>1. File (แฟ้ม) → Save As (บันทึกเป็น) → เลือกชนิดไฟล์ PDF</t>
+  </si>
+  <si>
+    <t>2. กดปุ่ม Options... (ตัวเลือก...) → เลือก Entire workbook (ทั้งเวิร์กบุ๊ก) → OK</t>
+  </si>
+  <si>
+    <t>3. กด Save (บันทึก)  — ข้อความนี้อยู่นอกขอบเขตพิมพ์ ไม่ติดไปใน PDF</t>
   </si>
 </sst>
 </file>
@@ -371,7 +383,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="13">
+  <fills count="12">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -388,12 +400,6 @@
       <patternFill patternType="solid">
         <fgColor rgb="FFF2F2F2"/>
         <bgColor rgb="FFEAF0FA"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF7F9FC"/>
-        <bgColor rgb="FFFFFFFF"/>
       </patternFill>
     </fill>
     <fill>
@@ -930,7 +936,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="146">
+  <cellXfs count="147">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -939,16 +945,16 @@
     <xf numFmtId="0" fontId="3" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -960,82 +966,301 @@
     <xf numFmtId="0" fontId="5" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="10" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="10" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="6" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="6" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="8" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="8" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="8" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="7" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="7" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="8" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="8" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="8" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="9" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="9" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="9" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="9" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="9" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="9" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="7" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="7" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="7" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1054,41 +1279,11 @@
     <xf numFmtId="0" fontId="5" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="9" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="9" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="9" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -1096,193 +1291,55 @@
     <xf numFmtId="0" fontId="5" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="8" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="8" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="8" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="10" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="10" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="10" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="10" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="10" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="10" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="10" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="10" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="10" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="10" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="10" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="10" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="9" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="9" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="9" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="9" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="9" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="9" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="9" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="3" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1294,66 +1351,16 @@
     <xf numFmtId="0" fontId="14" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="10" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="10" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="10" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="10" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="10" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="10" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="10" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="ปกติ" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="2">
     <dxf>
@@ -1537,15 +1544,15 @@
       <xdr:twoCellAnchor editAs="oneCell">
         <xdr:from>
           <xdr:col>4</xdr:col>
-          <xdr:colOff>51758</xdr:colOff>
+          <xdr:colOff>50800</xdr:colOff>
           <xdr:row>32</xdr:row>
-          <xdr:rowOff>172528</xdr:rowOff>
+          <xdr:rowOff>171450</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>4</xdr:col>
-          <xdr:colOff>664234</xdr:colOff>
+          <xdr:colOff>666750</xdr:colOff>
           <xdr:row>34</xdr:row>
-          <xdr:rowOff>8626</xdr:rowOff>
+          <xdr:rowOff>6350</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -1594,14 +1601,14 @@
             </a:extLst>
           </xdr:spPr>
           <xdr:txBody>
-            <a:bodyPr vertOverflow="clip" wrap="square" lIns="27432" tIns="22860" rIns="0" bIns="22860" anchor="ctr" upright="1"/>
+            <a:bodyPr vertOverflow="clip" wrap="square" lIns="36576" tIns="27432" rIns="0" bIns="27432" anchor="ctr" upright="1"/>
             <a:lstStyle/>
             <a:p>
               <a:pPr algn="l" rtl="0">
                 <a:defRPr sz="1000"/>
               </a:pPr>
               <a:r>
-                <a:rPr lang="th-TH" sz="800" b="0" i="0" u="none" strike="noStrike" baseline="0">
+                <a:rPr lang="en-US" sz="800" b="0" i="0" u="none" strike="noStrike" baseline="0">
                   <a:solidFill>
                     <a:srgbClr val="000000"/>
                   </a:solidFill>
@@ -1623,15 +1630,15 @@
       <xdr:twoCellAnchor editAs="oneCell">
         <xdr:from>
           <xdr:col>4</xdr:col>
-          <xdr:colOff>51758</xdr:colOff>
+          <xdr:colOff>50800</xdr:colOff>
           <xdr:row>33</xdr:row>
-          <xdr:rowOff>207034</xdr:rowOff>
+          <xdr:rowOff>209550</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>4</xdr:col>
-          <xdr:colOff>664234</xdr:colOff>
+          <xdr:colOff>666750</xdr:colOff>
           <xdr:row>35</xdr:row>
-          <xdr:rowOff>43132</xdr:rowOff>
+          <xdr:rowOff>44450</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -1680,14 +1687,14 @@
             </a:extLst>
           </xdr:spPr>
           <xdr:txBody>
-            <a:bodyPr vertOverflow="clip" wrap="square" lIns="27432" tIns="22860" rIns="0" bIns="22860" anchor="ctr" upright="1"/>
+            <a:bodyPr vertOverflow="clip" wrap="square" lIns="36576" tIns="27432" rIns="0" bIns="27432" anchor="ctr" upright="1"/>
             <a:lstStyle/>
             <a:p>
               <a:pPr algn="l" rtl="0">
                 <a:defRPr sz="1000"/>
               </a:pPr>
               <a:r>
-                <a:rPr lang="th-TH" sz="800" b="0" i="0" u="none" strike="noStrike" baseline="0">
+                <a:rPr lang="en-US" sz="800" b="0" i="0" u="none" strike="noStrike" baseline="0">
                   <a:solidFill>
                     <a:srgbClr val="000000"/>
                   </a:solidFill>
@@ -1709,15 +1716,15 @@
       <xdr:twoCellAnchor editAs="oneCell">
         <xdr:from>
           <xdr:col>5</xdr:col>
-          <xdr:colOff>25879</xdr:colOff>
+          <xdr:colOff>25400</xdr:colOff>
           <xdr:row>32</xdr:row>
-          <xdr:rowOff>172528</xdr:rowOff>
+          <xdr:rowOff>171450</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>5</xdr:col>
-          <xdr:colOff>638355</xdr:colOff>
+          <xdr:colOff>641350</xdr:colOff>
           <xdr:row>34</xdr:row>
-          <xdr:rowOff>8626</xdr:rowOff>
+          <xdr:rowOff>6350</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -1766,14 +1773,14 @@
             </a:extLst>
           </xdr:spPr>
           <xdr:txBody>
-            <a:bodyPr vertOverflow="clip" wrap="square" lIns="27432" tIns="22860" rIns="0" bIns="22860" anchor="ctr" upright="1"/>
+            <a:bodyPr vertOverflow="clip" wrap="square" lIns="36576" tIns="27432" rIns="0" bIns="27432" anchor="ctr" upright="1"/>
             <a:lstStyle/>
             <a:p>
               <a:pPr algn="l" rtl="0">
                 <a:defRPr sz="1000"/>
               </a:pPr>
               <a:r>
-                <a:rPr lang="th-TH" sz="800" b="0" i="0" u="none" strike="noStrike" baseline="0">
+                <a:rPr lang="en-US" sz="800" b="0" i="0" u="none" strike="noStrike" baseline="0">
                   <a:solidFill>
                     <a:srgbClr val="000000"/>
                   </a:solidFill>
@@ -1795,15 +1802,15 @@
       <xdr:twoCellAnchor editAs="oneCell">
         <xdr:from>
           <xdr:col>5</xdr:col>
-          <xdr:colOff>25879</xdr:colOff>
+          <xdr:colOff>25400</xdr:colOff>
           <xdr:row>33</xdr:row>
-          <xdr:rowOff>207034</xdr:rowOff>
+          <xdr:rowOff>209550</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>5</xdr:col>
-          <xdr:colOff>638355</xdr:colOff>
+          <xdr:colOff>641350</xdr:colOff>
           <xdr:row>35</xdr:row>
-          <xdr:rowOff>51758</xdr:rowOff>
+          <xdr:rowOff>50800</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -1852,14 +1859,14 @@
             </a:extLst>
           </xdr:spPr>
           <xdr:txBody>
-            <a:bodyPr vertOverflow="clip" wrap="square" lIns="27432" tIns="22860" rIns="0" bIns="22860" anchor="ctr" upright="1"/>
+            <a:bodyPr vertOverflow="clip" wrap="square" lIns="36576" tIns="27432" rIns="0" bIns="27432" anchor="ctr" upright="1"/>
             <a:lstStyle/>
             <a:p>
               <a:pPr algn="l" rtl="0">
                 <a:defRPr sz="1000"/>
               </a:pPr>
               <a:r>
-                <a:rPr lang="th-TH" sz="800" b="0" i="0" u="none" strike="noStrike" baseline="0">
+                <a:rPr lang="en-US" sz="800" b="0" i="0" u="none" strike="noStrike" baseline="0">
                   <a:solidFill>
                     <a:srgbClr val="000000"/>
                   </a:solidFill>
@@ -2170,236 +2177,228 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:J46"/>
-  <sheetFormatPr defaultColWidth="8.625" defaultRowHeight="17.7" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultColWidth="8.6328125" defaultRowHeight="17.5" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
-    <col min="1" max="1" width="4.625" style="1" customWidth="1"/>
-    <col min="2" max="2" width="16.625" style="1" customWidth="1"/>
-    <col min="3" max="3" width="15.875" style="1" customWidth="1"/>
-    <col min="4" max="5" width="9.875" style="1" customWidth="1"/>
-    <col min="6" max="7" width="16.625" style="1" customWidth="1"/>
-    <col min="8" max="8" width="23.75" style="1" customWidth="1"/>
-    <col min="9" max="16384" width="8.625" style="1"/>
+    <col min="1" max="1" width="4.6328125" style="1" customWidth="1"/>
+    <col min="2" max="2" width="16.6328125" style="1" customWidth="1"/>
+    <col min="3" max="3" width="15.90625" style="1" customWidth="1"/>
+    <col min="4" max="5" width="9.90625" style="1" customWidth="1"/>
+    <col min="6" max="7" width="16.6328125" style="1" customWidth="1"/>
+    <col min="8" max="8" width="23.7265625" style="1" customWidth="1"/>
+    <col min="9" max="16384" width="8.6328125" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="59.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A1" s="61" t="s">
+    <row r="1" spans="1:10" ht="60" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A1" s="107" t="s">
         <v>29</v>
       </c>
-      <c r="B1" s="61"/>
-      <c r="C1" s="61"/>
-      <c r="D1" s="61"/>
-      <c r="E1" s="61"/>
-      <c r="F1" s="61"/>
-      <c r="G1" s="61"/>
-      <c r="H1" s="61"/>
-    </row>
-    <row r="2" spans="1:10" ht="18.350000000000001" x14ac:dyDescent="0.4">
-      <c r="A2" s="49" t="s">
+      <c r="B1" s="107"/>
+      <c r="C1" s="107"/>
+      <c r="D1" s="107"/>
+      <c r="E1" s="107"/>
+      <c r="F1" s="107"/>
+      <c r="G1" s="107"/>
+      <c r="H1" s="107"/>
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+      <c r="A2" s="60" t="s">
         <v>53</v>
       </c>
-      <c r="B2" s="50"/>
-      <c r="C2" s="50"/>
-      <c r="D2" s="50"/>
-      <c r="E2" s="50"/>
-      <c r="F2" s="50"/>
-      <c r="G2" s="50"/>
-      <c r="H2" s="51"/>
-      <c r="J2" s="144" t="inlineStr">
-        <is>
-          <t xml:space="preserve">วิธีเซฟเป็น PDF ให้ได้ครบทุกหน้า (หน้าเอกสาร + หน้ารูปภาพ)</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.4">
-      <c r="A3" s="62" t="s">
+      <c r="B2" s="61"/>
+      <c r="C2" s="61"/>
+      <c r="D2" s="61"/>
+      <c r="E2" s="61"/>
+      <c r="F2" s="61"/>
+      <c r="G2" s="61"/>
+      <c r="H2" s="62"/>
+      <c r="J2" s="37" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+      <c r="A3" s="108" t="s">
         <v>69</v>
       </c>
-      <c r="B3" s="63"/>
-      <c r="C3" s="64"/>
-      <c r="D3" s="65"/>
-      <c r="E3" s="66"/>
-      <c r="F3" s="31" t="s">
+      <c r="B3" s="109"/>
+      <c r="C3" s="110"/>
+      <c r="D3" s="111"/>
+      <c r="E3" s="112"/>
+      <c r="F3" s="29" t="s">
         <v>32</v>
       </c>
-      <c r="G3" s="67"/>
-      <c r="H3" s="68"/>
-      <c r="J3" s="145" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1. File (แฟ้ม) → Save As (บันทึกเป็น) → เลือกชนิดไฟล์ PDF</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.4">
-      <c r="A4" s="69" t="s">
+      <c r="G3" s="79"/>
+      <c r="H3" s="80"/>
+      <c r="J3" s="38" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+      <c r="A4" s="39" t="s">
         <v>1</v>
       </c>
-      <c r="B4" s="70"/>
-      <c r="C4" s="71"/>
-      <c r="D4" s="72"/>
-      <c r="E4" s="73"/>
-      <c r="F4" s="32" t="s">
+      <c r="B4" s="40"/>
+      <c r="C4" s="97"/>
+      <c r="D4" s="98"/>
+      <c r="E4" s="99"/>
+      <c r="F4" s="30" t="s">
         <v>33</v>
       </c>
-      <c r="G4" s="74"/>
-      <c r="H4" s="75"/>
-      <c r="J4" s="145" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2. กดปุ่ม Options... (ตัวเลือก...) → เลือก Entire workbook (ทั้งเวิร์กบุ๊ก) → OK</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.4">
-      <c r="A5" s="69" t="s">
+      <c r="G4" s="82"/>
+      <c r="H4" s="83"/>
+      <c r="J4" s="38" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+      <c r="A5" s="39" t="s">
         <v>30</v>
       </c>
-      <c r="B5" s="70"/>
-      <c r="C5" s="82"/>
-      <c r="D5" s="117"/>
-      <c r="E5" s="118"/>
-      <c r="F5" s="33" t="s">
+      <c r="B5" s="40"/>
+      <c r="C5" s="41"/>
+      <c r="D5" s="42"/>
+      <c r="E5" s="43"/>
+      <c r="F5" s="31" t="s">
         <v>34</v>
       </c>
-      <c r="G5" s="82"/>
-      <c r="H5" s="83"/>
-      <c r="J5" s="145" t="inlineStr">
-        <is>
-          <t xml:space="preserve">3. กด Save (บันทึก)  — ข้อความนี้อยู่นอกขอบเขตพิมพ์ ไม่ติดไปใน PDF</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A6" s="119" t="s">
+      <c r="G5" s="41"/>
+      <c r="H5" s="103"/>
+      <c r="J5" s="38" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+      <c r="A6" s="52" t="s">
         <v>31</v>
       </c>
-      <c r="B6" s="120"/>
-      <c r="C6" s="121"/>
-      <c r="D6" s="122"/>
-      <c r="E6" s="123"/>
-      <c r="F6" s="34" t="s">
+      <c r="B6" s="53"/>
+      <c r="C6" s="54"/>
+      <c r="D6" s="55"/>
+      <c r="E6" s="56"/>
+      <c r="F6" s="32" t="s">
         <v>35</v>
       </c>
-      <c r="G6" s="47"/>
-      <c r="H6" s="48"/>
-    </row>
-    <row r="7" spans="1:8" ht="18.350000000000001" x14ac:dyDescent="0.4">
-      <c r="A7" s="49" t="s">
+      <c r="G6" s="64"/>
+      <c r="H6" s="65"/>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+      <c r="A7" s="60" t="s">
         <v>52</v>
       </c>
-      <c r="B7" s="50"/>
-      <c r="C7" s="50"/>
-      <c r="D7" s="50"/>
-      <c r="E7" s="50"/>
-      <c r="F7" s="50"/>
-      <c r="G7" s="50"/>
-      <c r="H7" s="51"/>
-    </row>
-    <row r="8" spans="1:8" ht="18.350000000000001" x14ac:dyDescent="0.4">
-      <c r="A8" s="52" t="s">
+      <c r="B7" s="61"/>
+      <c r="C7" s="61"/>
+      <c r="D7" s="61"/>
+      <c r="E7" s="61"/>
+      <c r="F7" s="61"/>
+      <c r="G7" s="61"/>
+      <c r="H7" s="62"/>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+      <c r="A8" s="120" t="s">
         <v>70</v>
       </c>
-      <c r="B8" s="53"/>
-      <c r="C8" s="53"/>
-      <c r="D8" s="53"/>
-      <c r="E8" s="53"/>
-      <c r="F8" s="35" t="s">
+      <c r="B8" s="121"/>
+      <c r="C8" s="121"/>
+      <c r="D8" s="121"/>
+      <c r="E8" s="121"/>
+      <c r="F8" s="33" t="s">
         <v>47</v>
       </c>
-      <c r="G8" s="35" t="s">
+      <c r="G8" s="33" t="s">
         <v>48</v>
       </c>
       <c r="H8" s="18"/>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A9" s="57" t="s">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+      <c r="A9" s="50" t="s">
         <v>2</v>
       </c>
-      <c r="B9" s="58"/>
-      <c r="C9" s="58"/>
-      <c r="D9" s="58"/>
-      <c r="E9" s="58"/>
+      <c r="B9" s="51"/>
+      <c r="C9" s="51"/>
+      <c r="D9" s="51"/>
+      <c r="E9" s="51"/>
       <c r="F9" s="6"/>
       <c r="G9" s="6"/>
       <c r="H9" s="7"/>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A10" s="57" t="s">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+      <c r="A10" s="50" t="s">
         <v>3</v>
       </c>
-      <c r="B10" s="58"/>
-      <c r="C10" s="58"/>
-      <c r="D10" s="58"/>
-      <c r="E10" s="58"/>
+      <c r="B10" s="51"/>
+      <c r="C10" s="51"/>
+      <c r="D10" s="51"/>
+      <c r="E10" s="51"/>
       <c r="F10" s="6"/>
       <c r="G10" s="6"/>
       <c r="H10" s="7"/>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A11" s="57" t="s">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+      <c r="A11" s="50" t="s">
         <v>4</v>
       </c>
-      <c r="B11" s="58"/>
-      <c r="C11" s="58"/>
-      <c r="D11" s="58"/>
-      <c r="E11" s="58"/>
+      <c r="B11" s="51"/>
+      <c r="C11" s="51"/>
+      <c r="D11" s="51"/>
+      <c r="E11" s="51"/>
       <c r="F11" s="6"/>
       <c r="G11" s="6"/>
       <c r="H11" s="7"/>
     </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A12" s="59" t="s">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+      <c r="A12" s="122" t="s">
         <v>5</v>
       </c>
-      <c r="B12" s="60"/>
-      <c r="C12" s="60"/>
-      <c r="D12" s="60"/>
-      <c r="E12" s="60"/>
+      <c r="B12" s="123"/>
+      <c r="C12" s="123"/>
+      <c r="D12" s="123"/>
+      <c r="E12" s="123"/>
       <c r="F12" s="16"/>
       <c r="G12" s="16"/>
       <c r="H12" s="17"/>
     </row>
-    <row r="13" spans="1:8" ht="18.350000000000001" x14ac:dyDescent="0.4">
-      <c r="A13" s="49" t="s">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+      <c r="A13" s="60" t="s">
         <v>54</v>
       </c>
-      <c r="B13" s="50"/>
-      <c r="C13" s="50"/>
-      <c r="D13" s="50"/>
-      <c r="E13" s="50"/>
-      <c r="F13" s="50"/>
-      <c r="G13" s="50"/>
-      <c r="H13" s="51"/>
-    </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A14" s="36" t="s">
+      <c r="B13" s="61"/>
+      <c r="C13" s="61"/>
+      <c r="D13" s="61"/>
+      <c r="E13" s="61"/>
+      <c r="F13" s="61"/>
+      <c r="G13" s="61"/>
+      <c r="H13" s="62"/>
+    </row>
+    <row r="14" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+      <c r="A14" s="34" t="s">
         <v>6</v>
       </c>
-      <c r="B14" s="84" t="s">
+      <c r="B14" s="104" t="s">
         <v>7</v>
       </c>
-      <c r="C14" s="85"/>
-      <c r="D14" s="86"/>
-      <c r="E14" s="37" t="s">
+      <c r="C14" s="105"/>
+      <c r="D14" s="106"/>
+      <c r="E14" s="35" t="s">
         <v>36</v>
       </c>
-      <c r="F14" s="37" t="s">
+      <c r="F14" s="35" t="s">
         <v>8</v>
       </c>
-      <c r="G14" s="37" t="s">
+      <c r="G14" s="35" t="s">
         <v>9</v>
       </c>
-      <c r="H14" s="38" t="s">
+      <c r="H14" s="36" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A15" s="2">
         <v>1</v>
       </c>
-      <c r="B15" s="54" t="s">
+      <c r="B15" s="44" t="s">
         <v>40</v>
       </c>
-      <c r="C15" s="55"/>
-      <c r="D15" s="56"/>
+      <c r="C15" s="45"/>
+      <c r="D15" s="46"/>
       <c r="E15" s="5" t="s">
         <v>37</v>
       </c>
@@ -2407,15 +2406,15 @@
       <c r="G15" s="4"/>
       <c r="H15" s="3"/>
     </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A16" s="2">
         <v>2</v>
       </c>
-      <c r="B16" s="54" t="s">
+      <c r="B16" s="44" t="s">
         <v>11</v>
       </c>
-      <c r="C16" s="55"/>
-      <c r="D16" s="56"/>
+      <c r="C16" s="45"/>
+      <c r="D16" s="46"/>
       <c r="E16" s="5" t="s">
         <v>37</v>
       </c>
@@ -2423,15 +2422,15 @@
       <c r="G16" s="4"/>
       <c r="H16" s="3"/>
     </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="17" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A17" s="2">
         <v>3</v>
       </c>
-      <c r="B17" s="54" t="s">
+      <c r="B17" s="44" t="s">
         <v>12</v>
       </c>
-      <c r="C17" s="55"/>
-      <c r="D17" s="56"/>
+      <c r="C17" s="45"/>
+      <c r="D17" s="46"/>
       <c r="E17" s="5" t="s">
         <v>37</v>
       </c>
@@ -2439,15 +2438,15 @@
       <c r="G17" s="4"/>
       <c r="H17" s="3"/>
     </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="18" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A18" s="2">
         <v>4</v>
       </c>
-      <c r="B18" s="54" t="s">
+      <c r="B18" s="44" t="s">
         <v>13</v>
       </c>
-      <c r="C18" s="55"/>
-      <c r="D18" s="56"/>
+      <c r="C18" s="45"/>
+      <c r="D18" s="46"/>
       <c r="E18" s="5" t="s">
         <v>37</v>
       </c>
@@ -2455,15 +2454,15 @@
       <c r="G18" s="4"/>
       <c r="H18" s="3"/>
     </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="19" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A19" s="2">
         <v>5</v>
       </c>
-      <c r="B19" s="54" t="s">
+      <c r="B19" s="44" t="s">
         <v>14</v>
       </c>
-      <c r="C19" s="55"/>
-      <c r="D19" s="56"/>
+      <c r="C19" s="45"/>
+      <c r="D19" s="46"/>
       <c r="E19" s="5" t="s">
         <v>37</v>
       </c>
@@ -2471,15 +2470,15 @@
       <c r="G19" s="4"/>
       <c r="H19" s="3"/>
     </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="20" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A20" s="2">
         <v>6</v>
       </c>
-      <c r="B20" s="54" t="s">
+      <c r="B20" s="44" t="s">
         <v>15</v>
       </c>
-      <c r="C20" s="55"/>
-      <c r="D20" s="56"/>
+      <c r="C20" s="45"/>
+      <c r="D20" s="46"/>
       <c r="E20" s="5" t="s">
         <v>37</v>
       </c>
@@ -2487,15 +2486,15 @@
       <c r="G20" s="4"/>
       <c r="H20" s="3"/>
     </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="21" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A21" s="2">
         <v>7</v>
       </c>
-      <c r="B21" s="54" t="s">
+      <c r="B21" s="44" t="s">
         <v>16</v>
       </c>
-      <c r="C21" s="55"/>
-      <c r="D21" s="56"/>
+      <c r="C21" s="45"/>
+      <c r="D21" s="46"/>
       <c r="E21" s="5" t="s">
         <v>37</v>
       </c>
@@ -2503,15 +2502,15 @@
       <c r="G21" s="4"/>
       <c r="H21" s="3"/>
     </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="22" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A22" s="2">
         <v>8</v>
       </c>
-      <c r="B22" s="54" t="s">
+      <c r="B22" s="44" t="s">
         <v>17</v>
       </c>
-      <c r="C22" s="55"/>
-      <c r="D22" s="56"/>
+      <c r="C22" s="45"/>
+      <c r="D22" s="46"/>
       <c r="E22" s="5" t="s">
         <v>37</v>
       </c>
@@ -2519,15 +2518,15 @@
       <c r="G22" s="4"/>
       <c r="H22" s="3"/>
     </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="23" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A23" s="2">
         <v>9</v>
       </c>
-      <c r="B23" s="54" t="s">
+      <c r="B23" s="44" t="s">
         <v>41</v>
       </c>
-      <c r="C23" s="55"/>
-      <c r="D23" s="56"/>
+      <c r="C23" s="45"/>
+      <c r="D23" s="46"/>
       <c r="E23" s="5" t="s">
         <v>37</v>
       </c>
@@ -2535,55 +2534,55 @@
       <c r="G23" s="4"/>
       <c r="H23" s="3"/>
     </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="24" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A24" s="2">
         <v>10</v>
       </c>
-      <c r="B24" s="54" t="s">
+      <c r="B24" s="44" t="s">
         <v>18</v>
       </c>
-      <c r="C24" s="55"/>
-      <c r="D24" s="56"/>
-      <c r="E24" s="30" t="s">
+      <c r="C24" s="45"/>
+      <c r="D24" s="46"/>
+      <c r="E24" s="28" t="s">
         <v>19</v>
       </c>
       <c r="F24" s="4"/>
       <c r="G24" s="4"/>
       <c r="H24" s="3"/>
     </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="25" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A25" s="2">
         <v>11</v>
       </c>
-      <c r="B25" s="54" t="s">
+      <c r="B25" s="44" t="s">
         <v>38</v>
       </c>
-      <c r="C25" s="55"/>
-      <c r="D25" s="56"/>
-      <c r="E25" s="30" t="s">
+      <c r="C25" s="45"/>
+      <c r="D25" s="46"/>
+      <c r="E25" s="28" t="s">
         <v>20</v>
       </c>
       <c r="F25" s="4"/>
       <c r="G25" s="4"/>
       <c r="H25" s="3"/>
     </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="26" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A26" s="2">
         <v>12</v>
       </c>
-      <c r="B26" s="54" t="s">
+      <c r="B26" s="44" t="s">
         <v>39</v>
       </c>
-      <c r="C26" s="55"/>
-      <c r="D26" s="56"/>
-      <c r="E26" s="30" t="s">
+      <c r="C26" s="45"/>
+      <c r="D26" s="46"/>
+      <c r="E26" s="28" t="s">
         <v>20</v>
       </c>
       <c r="F26" s="4"/>
       <c r="G26" s="4"/>
       <c r="H26" s="3"/>
     </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="27" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A27" s="2">
         <v>13</v>
       </c>
@@ -2592,22 +2591,22 @@
       </c>
       <c r="C27" s="9"/>
       <c r="D27" s="10"/>
-      <c r="E27" s="30" t="s">
+      <c r="E27" s="28" t="s">
         <v>68</v>
       </c>
       <c r="F27" s="4"/>
       <c r="G27" s="4"/>
       <c r="H27" s="3"/>
     </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="28" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A28" s="2">
         <v>14</v>
       </c>
-      <c r="B28" s="79" t="s">
+      <c r="B28" s="47" t="s">
         <v>43</v>
       </c>
-      <c r="C28" s="80"/>
-      <c r="D28" s="81"/>
+      <c r="C28" s="48"/>
+      <c r="D28" s="49"/>
       <c r="E28" s="5" t="s">
         <v>42</v>
       </c>
@@ -2615,15 +2614,15 @@
       <c r="G28" s="4"/>
       <c r="H28" s="3"/>
     </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="29" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A29" s="2">
         <v>15</v>
       </c>
-      <c r="B29" s="79" t="s">
+      <c r="B29" s="47" t="s">
         <v>44</v>
       </c>
-      <c r="C29" s="80"/>
-      <c r="D29" s="81"/>
+      <c r="C29" s="48"/>
+      <c r="D29" s="49"/>
       <c r="E29" s="5" t="s">
         <v>45</v>
       </c>
@@ -2631,15 +2630,15 @@
       <c r="G29" s="4"/>
       <c r="H29" s="3"/>
     </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="30" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A30" s="2">
         <v>16</v>
       </c>
-      <c r="B30" s="54" t="s">
+      <c r="B30" s="44" t="s">
         <v>21</v>
       </c>
-      <c r="C30" s="55"/>
-      <c r="D30" s="56"/>
+      <c r="C30" s="45"/>
+      <c r="D30" s="46"/>
       <c r="E30" s="5" t="s">
         <v>46</v>
       </c>
@@ -2647,15 +2646,15 @@
       <c r="G30" s="4"/>
       <c r="H30" s="3"/>
     </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="31" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A31" s="2">
         <v>17</v>
       </c>
-      <c r="B31" s="54" t="s">
+      <c r="B31" s="44" t="s">
         <v>22</v>
       </c>
-      <c r="C31" s="55"/>
-      <c r="D31" s="56"/>
+      <c r="C31" s="45"/>
+      <c r="D31" s="46"/>
       <c r="E31" s="5" t="s">
         <v>37</v>
       </c>
@@ -2663,15 +2662,15 @@
       <c r="G31" s="4"/>
       <c r="H31" s="3"/>
     </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="32" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A32" s="2">
         <v>18</v>
       </c>
-      <c r="B32" s="76" t="s">
+      <c r="B32" s="100" t="s">
         <v>23</v>
       </c>
-      <c r="C32" s="77"/>
-      <c r="D32" s="78"/>
+      <c r="C32" s="101"/>
+      <c r="D32" s="102"/>
       <c r="E32" s="13" t="s">
         <v>37</v>
       </c>
@@ -2679,188 +2678,215 @@
       <c r="G32" s="14"/>
       <c r="H32" s="15"/>
     </row>
-    <row r="33" spans="1:8" ht="18.350000000000001" x14ac:dyDescent="0.4">
-      <c r="A33" s="49" t="s">
+    <row r="33" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A33" s="60" t="s">
         <v>49</v>
       </c>
-      <c r="B33" s="50"/>
-      <c r="C33" s="50"/>
-      <c r="D33" s="50"/>
-      <c r="E33" s="50"/>
-      <c r="F33" s="50"/>
-      <c r="G33" s="50"/>
-      <c r="H33" s="51"/>
-    </row>
-    <row r="34" spans="1:8" ht="18.350000000000001" x14ac:dyDescent="0.4">
-      <c r="A34" s="91" t="s">
+      <c r="B33" s="61"/>
+      <c r="C33" s="61"/>
+      <c r="D33" s="61"/>
+      <c r="E33" s="61"/>
+      <c r="F33" s="61"/>
+      <c r="G33" s="61"/>
+      <c r="H33" s="62"/>
+    </row>
+    <row r="34" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A34" s="66" t="s">
         <v>50</v>
       </c>
-      <c r="B34" s="92"/>
-      <c r="C34" s="93"/>
+      <c r="B34" s="67"/>
+      <c r="C34" s="68"/>
       <c r="D34" s="11" t="s">
         <v>8</v>
       </c>
-      <c r="E34" s="97"/>
-      <c r="F34" s="98"/>
-      <c r="G34" s="98"/>
-      <c r="H34" s="99"/>
-    </row>
-    <row r="35" spans="1:8" ht="18.350000000000001" x14ac:dyDescent="0.4">
-      <c r="A35" s="94" t="s">
+      <c r="E34" s="72"/>
+      <c r="F34" s="73"/>
+      <c r="G34" s="73"/>
+      <c r="H34" s="74"/>
+    </row>
+    <row r="35" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A35" s="69" t="s">
         <v>50</v>
       </c>
-      <c r="B35" s="95"/>
-      <c r="C35" s="96"/>
+      <c r="B35" s="70"/>
+      <c r="C35" s="71"/>
       <c r="D35" s="12" t="s">
         <v>9</v>
       </c>
-      <c r="E35" s="100"/>
-      <c r="F35" s="101"/>
-      <c r="G35" s="101"/>
-      <c r="H35" s="102"/>
-    </row>
-    <row r="36" spans="1:8" ht="18.350000000000001" x14ac:dyDescent="0.4">
-      <c r="A36" s="49" t="s">
+      <c r="E35" s="75"/>
+      <c r="F35" s="76"/>
+      <c r="G35" s="76"/>
+      <c r="H35" s="77"/>
+    </row>
+    <row r="36" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A36" s="60" t="s">
         <v>51</v>
       </c>
-      <c r="B36" s="50"/>
-      <c r="C36" s="50"/>
-      <c r="D36" s="50"/>
-      <c r="E36" s="50"/>
-      <c r="F36" s="50"/>
-      <c r="G36" s="50"/>
-      <c r="H36" s="51"/>
-    </row>
-    <row r="37" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A37" s="103"/>
-      <c r="B37" s="67"/>
-      <c r="C37" s="67"/>
-      <c r="D37" s="67"/>
-      <c r="E37" s="67"/>
-      <c r="F37" s="67"/>
-      <c r="G37" s="67"/>
-      <c r="H37" s="68"/>
-    </row>
-    <row r="38" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A38" s="104"/>
-      <c r="B38" s="74"/>
-      <c r="C38" s="74"/>
-      <c r="D38" s="74"/>
-      <c r="E38" s="74"/>
-      <c r="F38" s="74"/>
-      <c r="G38" s="74"/>
-      <c r="H38" s="75"/>
-    </row>
-    <row r="39" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A39" s="104"/>
-      <c r="B39" s="74"/>
-      <c r="C39" s="74"/>
-      <c r="D39" s="74"/>
-      <c r="E39" s="74"/>
-      <c r="F39" s="74"/>
-      <c r="G39" s="74"/>
-      <c r="H39" s="75"/>
-    </row>
-    <row r="40" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A40" s="90"/>
-      <c r="B40" s="47"/>
-      <c r="C40" s="47"/>
-      <c r="D40" s="47"/>
-      <c r="E40" s="47"/>
-      <c r="F40" s="47"/>
-      <c r="G40" s="47"/>
-      <c r="H40" s="48"/>
-    </row>
-    <row r="41" spans="1:8" ht="18.350000000000001" x14ac:dyDescent="0.4">
-      <c r="A41" s="49" t="s">
+      <c r="B36" s="61"/>
+      <c r="C36" s="61"/>
+      <c r="D36" s="61"/>
+      <c r="E36" s="61"/>
+      <c r="F36" s="61"/>
+      <c r="G36" s="61"/>
+      <c r="H36" s="62"/>
+    </row>
+    <row r="37" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A37" s="78"/>
+      <c r="B37" s="79"/>
+      <c r="C37" s="79"/>
+      <c r="D37" s="79"/>
+      <c r="E37" s="79"/>
+      <c r="F37" s="79"/>
+      <c r="G37" s="79"/>
+      <c r="H37" s="80"/>
+    </row>
+    <row r="38" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A38" s="81"/>
+      <c r="B38" s="82"/>
+      <c r="C38" s="82"/>
+      <c r="D38" s="82"/>
+      <c r="E38" s="82"/>
+      <c r="F38" s="82"/>
+      <c r="G38" s="82"/>
+      <c r="H38" s="83"/>
+    </row>
+    <row r="39" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A39" s="81"/>
+      <c r="B39" s="82"/>
+      <c r="C39" s="82"/>
+      <c r="D39" s="82"/>
+      <c r="E39" s="82"/>
+      <c r="F39" s="82"/>
+      <c r="G39" s="82"/>
+      <c r="H39" s="83"/>
+    </row>
+    <row r="40" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A40" s="63"/>
+      <c r="B40" s="64"/>
+      <c r="C40" s="64"/>
+      <c r="D40" s="64"/>
+      <c r="E40" s="64"/>
+      <c r="F40" s="64"/>
+      <c r="G40" s="64"/>
+      <c r="H40" s="65"/>
+    </row>
+    <row r="41" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A41" s="60" t="s">
         <v>66</v>
       </c>
-      <c r="B41" s="50"/>
-      <c r="C41" s="50"/>
-      <c r="D41" s="50"/>
-      <c r="E41" s="50"/>
-      <c r="F41" s="50"/>
-      <c r="G41" s="50"/>
-      <c r="H41" s="51"/>
-    </row>
-    <row r="42" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A42" s="105" t="s">
+      <c r="B41" s="61"/>
+      <c r="C41" s="61"/>
+      <c r="D41" s="61"/>
+      <c r="E41" s="61"/>
+      <c r="F41" s="61"/>
+      <c r="G41" s="61"/>
+      <c r="H41" s="62"/>
+    </row>
+    <row r="42" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A42" s="84" t="s">
         <v>24</v>
       </c>
-      <c r="B42" s="106"/>
-      <c r="C42" s="106"/>
-      <c r="D42" s="106"/>
-      <c r="E42" s="107"/>
-      <c r="F42" s="108" t="s">
+      <c r="B42" s="85"/>
+      <c r="C42" s="85"/>
+      <c r="D42" s="85"/>
+      <c r="E42" s="86"/>
+      <c r="F42" s="87" t="s">
         <v>25</v>
       </c>
-      <c r="G42" s="106"/>
-      <c r="H42" s="109"/>
-    </row>
-    <row r="43" spans="1:8" ht="25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A43" s="110" t="s">
+      <c r="G42" s="85"/>
+      <c r="H42" s="88"/>
+    </row>
+    <row r="43" spans="1:8" ht="25" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A43" s="89" t="s">
         <v>26</v>
       </c>
-      <c r="B43" s="111"/>
-      <c r="C43" s="111"/>
-      <c r="D43" s="111"/>
-      <c r="E43" s="112"/>
-      <c r="F43" s="113" t="s">
+      <c r="B43" s="90"/>
+      <c r="C43" s="90"/>
+      <c r="D43" s="90"/>
+      <c r="E43" s="91"/>
+      <c r="F43" s="92" t="s">
         <v>26</v>
       </c>
-      <c r="G43" s="111"/>
-      <c r="H43" s="114"/>
-    </row>
-    <row r="44" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A44" s="115" t="s">
+      <c r="G43" s="90"/>
+      <c r="H43" s="93"/>
+    </row>
+    <row r="44" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A44" s="94" t="s">
         <v>27</v>
       </c>
-      <c r="B44" s="40"/>
-      <c r="C44" s="40"/>
-      <c r="D44" s="40"/>
-      <c r="E44" s="116"/>
-      <c r="F44" s="39" t="s">
+      <c r="B44" s="95"/>
+      <c r="C44" s="95"/>
+      <c r="D44" s="95"/>
+      <c r="E44" s="96"/>
+      <c r="F44" s="113" t="s">
         <v>28</v>
       </c>
-      <c r="G44" s="40"/>
-      <c r="H44" s="41"/>
-    </row>
-    <row r="45" spans="1:8" ht="25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A45" s="42" t="s">
+      <c r="G44" s="95"/>
+      <c r="H44" s="114"/>
+    </row>
+    <row r="45" spans="1:8" ht="25" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A45" s="115" t="s">
         <v>26</v>
       </c>
-      <c r="B45" s="43"/>
-      <c r="C45" s="43"/>
-      <c r="D45" s="43"/>
-      <c r="E45" s="44"/>
-      <c r="F45" s="45" t="s">
+      <c r="B45" s="116"/>
+      <c r="C45" s="116"/>
+      <c r="D45" s="116"/>
+      <c r="E45" s="117"/>
+      <c r="F45" s="118" t="s">
         <v>26</v>
       </c>
-      <c r="G45" s="43"/>
-      <c r="H45" s="46"/>
-    </row>
-    <row r="46" spans="1:8" ht="36" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A46" s="87" t="s">
+      <c r="G45" s="116"/>
+      <c r="H45" s="119"/>
+    </row>
+    <row r="46" spans="1:8" ht="36" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A46" s="57" t="s">
         <v>55</v>
       </c>
-      <c r="B46" s="88"/>
-      <c r="C46" s="88"/>
-      <c r="D46" s="88"/>
-      <c r="E46" s="88"/>
-      <c r="F46" s="88"/>
-      <c r="G46" s="88"/>
-      <c r="H46" s="89"/>
+      <c r="B46" s="58"/>
+      <c r="C46" s="58"/>
+      <c r="D46" s="58"/>
+      <c r="E46" s="58"/>
+      <c r="F46" s="58"/>
+      <c r="G46" s="58"/>
+      <c r="H46" s="59"/>
     </row>
   </sheetData>
   <mergeCells count="59">
-    <mergeCell ref="A5:B5"/>
-    <mergeCell ref="C5:E5"/>
-    <mergeCell ref="B25:D25"/>
-    <mergeCell ref="B26:D26"/>
-    <mergeCell ref="B28:D28"/>
-    <mergeCell ref="A9:E9"/>
-    <mergeCell ref="A6:B6"/>
-    <mergeCell ref="C6:E6"/>
+    <mergeCell ref="F44:H44"/>
+    <mergeCell ref="A45:E45"/>
+    <mergeCell ref="F45:H45"/>
+    <mergeCell ref="G6:H6"/>
+    <mergeCell ref="A7:H7"/>
+    <mergeCell ref="A8:E8"/>
+    <mergeCell ref="B19:D19"/>
+    <mergeCell ref="B21:D21"/>
+    <mergeCell ref="B22:D22"/>
+    <mergeCell ref="B23:D23"/>
+    <mergeCell ref="B24:D24"/>
+    <mergeCell ref="A10:E10"/>
+    <mergeCell ref="A11:E11"/>
+    <mergeCell ref="A12:E12"/>
+    <mergeCell ref="A1:H1"/>
+    <mergeCell ref="A2:H2"/>
+    <mergeCell ref="A3:B3"/>
+    <mergeCell ref="C3:E3"/>
+    <mergeCell ref="G3:H3"/>
+    <mergeCell ref="A4:B4"/>
+    <mergeCell ref="C4:E4"/>
+    <mergeCell ref="G4:H4"/>
+    <mergeCell ref="A33:H33"/>
+    <mergeCell ref="B31:D31"/>
+    <mergeCell ref="B32:D32"/>
+    <mergeCell ref="B30:D30"/>
+    <mergeCell ref="A13:H13"/>
+    <mergeCell ref="B29:D29"/>
+    <mergeCell ref="G5:H5"/>
+    <mergeCell ref="B14:D14"/>
+    <mergeCell ref="B15:D15"/>
+    <mergeCell ref="B16:D16"/>
+    <mergeCell ref="B17:D17"/>
+    <mergeCell ref="B18:D18"/>
+    <mergeCell ref="B20:D20"/>
     <mergeCell ref="A46:H46"/>
     <mergeCell ref="A36:H36"/>
     <mergeCell ref="A40:H40"/>
@@ -2877,41 +2903,14 @@
     <mergeCell ref="A43:E43"/>
     <mergeCell ref="F43:H43"/>
     <mergeCell ref="A44:E44"/>
-    <mergeCell ref="A4:B4"/>
-    <mergeCell ref="C4:E4"/>
-    <mergeCell ref="G4:H4"/>
-    <mergeCell ref="A33:H33"/>
-    <mergeCell ref="B31:D31"/>
-    <mergeCell ref="B32:D32"/>
-    <mergeCell ref="B30:D30"/>
-    <mergeCell ref="A13:H13"/>
-    <mergeCell ref="B29:D29"/>
-    <mergeCell ref="G5:H5"/>
-    <mergeCell ref="B14:D14"/>
-    <mergeCell ref="B15:D15"/>
-    <mergeCell ref="B16:D16"/>
-    <mergeCell ref="B17:D17"/>
-    <mergeCell ref="B18:D18"/>
-    <mergeCell ref="B20:D20"/>
-    <mergeCell ref="A1:H1"/>
-    <mergeCell ref="A2:H2"/>
-    <mergeCell ref="A3:B3"/>
-    <mergeCell ref="C3:E3"/>
-    <mergeCell ref="G3:H3"/>
-    <mergeCell ref="F44:H44"/>
-    <mergeCell ref="A45:E45"/>
-    <mergeCell ref="F45:H45"/>
-    <mergeCell ref="G6:H6"/>
-    <mergeCell ref="A7:H7"/>
-    <mergeCell ref="A8:E8"/>
-    <mergeCell ref="B19:D19"/>
-    <mergeCell ref="B21:D21"/>
-    <mergeCell ref="B22:D22"/>
-    <mergeCell ref="B23:D23"/>
-    <mergeCell ref="B24:D24"/>
-    <mergeCell ref="A10:E10"/>
-    <mergeCell ref="A11:E11"/>
-    <mergeCell ref="A12:E12"/>
+    <mergeCell ref="A5:B5"/>
+    <mergeCell ref="C5:E5"/>
+    <mergeCell ref="B25:D25"/>
+    <mergeCell ref="B26:D26"/>
+    <mergeCell ref="B28:D28"/>
+    <mergeCell ref="A9:E9"/>
+    <mergeCell ref="A6:B6"/>
+    <mergeCell ref="C6:E6"/>
   </mergeCells>
   <conditionalFormatting sqref="F15:G32">
     <cfRule type="cellIs" dxfId="1" priority="4" operator="equal">
@@ -2942,15 +2941,15 @@
                 <anchor moveWithCells="1">
                   <from>
                     <xdr:col>4</xdr:col>
-                    <xdr:colOff>51758</xdr:colOff>
+                    <xdr:colOff>50800</xdr:colOff>
                     <xdr:row>32</xdr:row>
-                    <xdr:rowOff>172528</xdr:rowOff>
+                    <xdr:rowOff>171450</xdr:rowOff>
                   </from>
                   <to>
                     <xdr:col>4</xdr:col>
-                    <xdr:colOff>664234</xdr:colOff>
+                    <xdr:colOff>666750</xdr:colOff>
                     <xdr:row>34</xdr:row>
-                    <xdr:rowOff>8626</xdr:rowOff>
+                    <xdr:rowOff>6350</xdr:rowOff>
                   </to>
                 </anchor>
               </controlPr>
@@ -2964,15 +2963,15 @@
                 <anchor moveWithCells="1">
                   <from>
                     <xdr:col>4</xdr:col>
-                    <xdr:colOff>51758</xdr:colOff>
+                    <xdr:colOff>50800</xdr:colOff>
                     <xdr:row>33</xdr:row>
-                    <xdr:rowOff>207034</xdr:rowOff>
+                    <xdr:rowOff>209550</xdr:rowOff>
                   </from>
                   <to>
                     <xdr:col>4</xdr:col>
-                    <xdr:colOff>664234</xdr:colOff>
+                    <xdr:colOff>666750</xdr:colOff>
                     <xdr:row>35</xdr:row>
-                    <xdr:rowOff>43132</xdr:rowOff>
+                    <xdr:rowOff>44450</xdr:rowOff>
                   </to>
                 </anchor>
               </controlPr>
@@ -2986,15 +2985,15 @@
                 <anchor moveWithCells="1">
                   <from>
                     <xdr:col>5</xdr:col>
-                    <xdr:colOff>25879</xdr:colOff>
+                    <xdr:colOff>25400</xdr:colOff>
                     <xdr:row>32</xdr:row>
-                    <xdr:rowOff>172528</xdr:rowOff>
+                    <xdr:rowOff>171450</xdr:rowOff>
                   </from>
                   <to>
                     <xdr:col>5</xdr:col>
-                    <xdr:colOff>638355</xdr:colOff>
+                    <xdr:colOff>641350</xdr:colOff>
                     <xdr:row>34</xdr:row>
-                    <xdr:rowOff>8626</xdr:rowOff>
+                    <xdr:rowOff>6350</xdr:rowOff>
                   </to>
                 </anchor>
               </controlPr>
@@ -3008,15 +3007,15 @@
                 <anchor moveWithCells="1">
                   <from>
                     <xdr:col>5</xdr:col>
-                    <xdr:colOff>25879</xdr:colOff>
+                    <xdr:colOff>25400</xdr:colOff>
                     <xdr:row>33</xdr:row>
-                    <xdr:rowOff>207034</xdr:rowOff>
+                    <xdr:rowOff>209550</xdr:rowOff>
                   </from>
                   <to>
                     <xdr:col>5</xdr:col>
-                    <xdr:colOff>638355</xdr:colOff>
+                    <xdr:colOff>641350</xdr:colOff>
                     <xdr:row>35</xdr:row>
-                    <xdr:rowOff>51758</xdr:rowOff>
+                    <xdr:rowOff>50800</xdr:rowOff>
                   </to>
                 </anchor>
               </controlPr>
@@ -3032,58 +3031,56 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{51496EA4-4132-4452-9309-55127D2AD8A7}">
   <dimension ref="A1:L36"/>
-  <sheetFormatPr defaultColWidth="8.625" defaultRowHeight="17.7" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultColWidth="8.6328125" defaultRowHeight="17.5" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
-    <col min="1" max="1" width="2.625" style="1" customWidth="1"/>
-    <col min="2" max="3" width="12.625" style="1" customWidth="1"/>
-    <col min="4" max="4" width="2.625" style="1" customWidth="1"/>
-    <col min="5" max="6" width="12.625" style="1" customWidth="1"/>
-    <col min="7" max="7" width="2.625" style="1" customWidth="1"/>
-    <col min="8" max="9" width="12.625" style="1" customWidth="1"/>
-    <col min="10" max="10" width="2.625" style="1" customWidth="1"/>
-    <col min="11" max="16384" width="8.625" style="1"/>
+    <col min="1" max="1" width="2.6328125" style="1" customWidth="1"/>
+    <col min="2" max="3" width="12.6328125" style="1" customWidth="1"/>
+    <col min="4" max="4" width="2.6328125" style="1" customWidth="1"/>
+    <col min="5" max="6" width="12.6328125" style="1" customWidth="1"/>
+    <col min="7" max="7" width="2.6328125" style="1" customWidth="1"/>
+    <col min="8" max="9" width="12.6328125" style="1" customWidth="1"/>
+    <col min="10" max="10" width="2.6328125" style="1" customWidth="1"/>
+    <col min="11" max="16384" width="8.6328125" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="56.4" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A1" s="134" t="s">
+    <row r="1" spans="1:12" ht="56.4" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A1" s="131" t="s">
         <v>62</v>
       </c>
-      <c r="B1" s="135"/>
-      <c r="C1" s="135"/>
-      <c r="D1" s="135"/>
-      <c r="E1" s="135"/>
-      <c r="F1" s="135"/>
-      <c r="G1" s="135"/>
-      <c r="H1" s="135"/>
-      <c r="I1" s="135"/>
-      <c r="J1" s="136"/>
-    </row>
-    <row r="2" spans="1:12" ht="21.1" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A2" s="137" t="s">
+      <c r="B1" s="132"/>
+      <c r="C1" s="132"/>
+      <c r="D1" s="132"/>
+      <c r="E1" s="132"/>
+      <c r="F1" s="132"/>
+      <c r="G1" s="132"/>
+      <c r="H1" s="132"/>
+      <c r="I1" s="132"/>
+      <c r="J1" s="133"/>
+    </row>
+    <row r="2" spans="1:12" ht="21.15" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A2" s="134" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="138"/>
-      <c r="C2" s="139" t="s">
+      <c r="B2" s="135"/>
+      <c r="C2" s="136" t="s">
         <v>56</v>
       </c>
-      <c r="D2" s="140"/>
-      <c r="E2" s="141"/>
-      <c r="F2" s="142" t="s">
+      <c r="D2" s="137"/>
+      <c r="E2" s="138"/>
+      <c r="F2" s="139" t="s">
         <v>30</v>
       </c>
-      <c r="G2" s="143"/>
-      <c r="H2" s="139" t="s">
+      <c r="G2" s="140"/>
+      <c r="H2" s="136" t="s">
         <v>56</v>
       </c>
-      <c r="I2" s="140"/>
-      <c r="J2" s="141"/>
-      <c r="L2" s="144" t="inlineStr">
-        <is>
-          <t xml:space="preserve">วิธีเซฟเป็น PDF ให้ได้ครบทุกหน้า (หน้าเอกสาร + หน้ารูปภาพ)</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" spans="1:12" ht="18.350000000000001" x14ac:dyDescent="0.4">
+      <c r="I2" s="137"/>
+      <c r="J2" s="138"/>
+      <c r="L2" s="37" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12" x14ac:dyDescent="0.55000000000000004">
       <c r="A3" s="19"/>
       <c r="B3" s="20"/>
       <c r="C3" s="20"/>
@@ -3094,455 +3091,436 @@
       <c r="H3" s="20"/>
       <c r="I3" s="20"/>
       <c r="J3" s="21"/>
-      <c r="L3" s="145" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1. File (แฟ้ม) → Save As (บันทึกเป็น) → เลือกชนิดไฟล์ PDF</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" spans="1:12" ht="18.350000000000001" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="L3" s="38" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" ht="18.399999999999999" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A4" s="19"/>
-      <c r="B4" s="127" t="s">
+      <c r="B4" s="124" t="s">
         <v>57</v>
       </c>
-      <c r="C4" s="128"/>
-      <c r="D4" s="22"/>
-      <c r="E4" s="133" t="s">
+      <c r="C4" s="125"/>
+      <c r="D4" s="144"/>
+      <c r="E4" s="130" t="s">
         <v>57</v>
       </c>
-      <c r="F4" s="133"/>
-      <c r="H4" s="133" t="s">
+      <c r="F4" s="130"/>
+      <c r="H4" s="130" t="s">
         <v>57</v>
       </c>
-      <c r="I4" s="133"/>
+      <c r="I4" s="130"/>
       <c r="J4" s="21"/>
-      <c r="L4" s="145" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2. กดปุ่ม Options... (ตัวเลือก...) → เลือก Entire workbook (ทั้งเวิร์กบุ๊ก) → OK</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" spans="1:12" ht="18.350000000000001" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="L4" s="38" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" ht="18.399999999999999" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A5" s="19"/>
-      <c r="B5" s="129"/>
-      <c r="C5" s="130"/>
-      <c r="D5" s="22"/>
-      <c r="E5" s="133"/>
-      <c r="F5" s="133"/>
-      <c r="H5" s="133"/>
-      <c r="I5" s="133"/>
+      <c r="B5" s="126"/>
+      <c r="C5" s="127"/>
+      <c r="D5" s="144"/>
+      <c r="E5" s="130"/>
+      <c r="F5" s="130"/>
+      <c r="H5" s="130"/>
+      <c r="I5" s="130"/>
       <c r="J5" s="21"/>
-      <c r="L5" s="145" t="inlineStr">
-        <is>
-          <t xml:space="preserve">3. กด Save (บันทึก)  — ข้อความนี้อยู่นอกขอบเขตพิมพ์ ไม่ติดไปใน PDF</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" spans="1:10" ht="18.350000000000001" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="L5" s="38" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" ht="18.399999999999999" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A6" s="19"/>
-      <c r="B6" s="129"/>
-      <c r="C6" s="130"/>
-      <c r="D6" s="22"/>
-      <c r="E6" s="133"/>
-      <c r="F6" s="133"/>
-      <c r="H6" s="133"/>
-      <c r="I6" s="133"/>
+      <c r="B6" s="126"/>
+      <c r="C6" s="127"/>
+      <c r="D6" s="144"/>
+      <c r="E6" s="130"/>
+      <c r="F6" s="130"/>
+      <c r="H6" s="130"/>
+      <c r="I6" s="130"/>
       <c r="J6" s="21"/>
     </row>
-    <row r="7" spans="1:10" ht="18.350000000000001" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:12" ht="18.399999999999999" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A7" s="19"/>
-      <c r="B7" s="129"/>
-      <c r="C7" s="130"/>
-      <c r="D7" s="22"/>
-      <c r="E7" s="133"/>
-      <c r="F7" s="133"/>
-      <c r="H7" s="133"/>
-      <c r="I7" s="133"/>
+      <c r="B7" s="126"/>
+      <c r="C7" s="127"/>
+      <c r="D7" s="144"/>
+      <c r="E7" s="130"/>
+      <c r="F7" s="130"/>
+      <c r="H7" s="130"/>
+      <c r="I7" s="130"/>
       <c r="J7" s="21"/>
     </row>
-    <row r="8" spans="1:10" ht="18.350000000000001" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:12" ht="18.399999999999999" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A8" s="19"/>
-      <c r="B8" s="129"/>
-      <c r="C8" s="130"/>
-      <c r="D8" s="22"/>
-      <c r="E8" s="133"/>
-      <c r="F8" s="133"/>
-      <c r="H8" s="133"/>
-      <c r="I8" s="133"/>
+      <c r="B8" s="126"/>
+      <c r="C8" s="127"/>
+      <c r="D8" s="144"/>
+      <c r="E8" s="130"/>
+      <c r="F8" s="130"/>
+      <c r="H8" s="130"/>
+      <c r="I8" s="130"/>
       <c r="J8" s="21"/>
     </row>
-    <row r="9" spans="1:10" ht="17.7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:12" ht="17.75" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A9" s="19"/>
-      <c r="B9" s="129"/>
-      <c r="C9" s="130"/>
-      <c r="D9" s="23"/>
-      <c r="E9" s="133"/>
-      <c r="F9" s="133"/>
-      <c r="G9" s="24" t="s">
+      <c r="B9" s="126"/>
+      <c r="C9" s="127"/>
+      <c r="D9" s="145"/>
+      <c r="E9" s="130"/>
+      <c r="F9" s="130"/>
+      <c r="G9" s="22" t="s">
         <v>58</v>
       </c>
-      <c r="H9" s="133"/>
-      <c r="I9" s="133"/>
+      <c r="H9" s="130"/>
+      <c r="I9" s="130"/>
       <c r="J9" s="21"/>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:12" x14ac:dyDescent="0.55000000000000004">
       <c r="A10" s="19"/>
-      <c r="B10" s="129"/>
-      <c r="C10" s="130"/>
-      <c r="D10" s="23"/>
-      <c r="E10" s="133"/>
-      <c r="F10" s="133"/>
-      <c r="G10" s="24"/>
-      <c r="H10" s="133"/>
-      <c r="I10" s="133"/>
+      <c r="B10" s="126"/>
+      <c r="C10" s="127"/>
+      <c r="D10" s="145"/>
+      <c r="E10" s="130"/>
+      <c r="F10" s="130"/>
+      <c r="G10" s="22"/>
+      <c r="H10" s="130"/>
+      <c r="I10" s="130"/>
       <c r="J10" s="21"/>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:12" x14ac:dyDescent="0.55000000000000004">
       <c r="A11" s="19"/>
-      <c r="B11" s="129"/>
-      <c r="C11" s="130"/>
-      <c r="D11" s="23"/>
-      <c r="E11" s="133"/>
-      <c r="F11" s="133"/>
-      <c r="G11" s="24"/>
-      <c r="H11" s="133"/>
-      <c r="I11" s="133"/>
+      <c r="B11" s="126"/>
+      <c r="C11" s="127"/>
+      <c r="D11" s="145"/>
+      <c r="E11" s="130"/>
+      <c r="F11" s="130"/>
+      <c r="G11" s="22"/>
+      <c r="H11" s="130"/>
+      <c r="I11" s="130"/>
       <c r="J11" s="21"/>
     </row>
-    <row r="12" spans="1:10" ht="17.7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:12" ht="17.75" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A12" s="19"/>
-      <c r="B12" s="131"/>
-      <c r="C12" s="132"/>
-      <c r="D12" s="23"/>
-      <c r="E12" s="133"/>
-      <c r="F12" s="133"/>
-      <c r="G12" s="24"/>
-      <c r="H12" s="133"/>
-      <c r="I12" s="133"/>
+      <c r="B12" s="128"/>
+      <c r="C12" s="129"/>
+      <c r="D12" s="145"/>
+      <c r="E12" s="130"/>
+      <c r="F12" s="130"/>
+      <c r="G12" s="22"/>
+      <c r="H12" s="130"/>
+      <c r="I12" s="130"/>
       <c r="J12" s="21"/>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:12" x14ac:dyDescent="0.55000000000000004">
       <c r="A13" s="19"/>
-      <c r="B13" s="124" t="s">
+      <c r="B13" s="141" t="s">
         <v>71</v>
       </c>
-      <c r="C13" s="125"/>
-      <c r="D13" s="23"/>
-      <c r="E13" s="126" t="s">
+      <c r="C13" s="142"/>
+      <c r="D13" s="145"/>
+      <c r="E13" s="143" t="s">
         <v>63</v>
       </c>
-      <c r="F13" s="126"/>
-      <c r="G13" s="24"/>
-      <c r="H13" s="126" t="s">
+      <c r="F13" s="143"/>
+      <c r="G13" s="22"/>
+      <c r="H13" s="143" t="s">
         <v>63</v>
       </c>
-      <c r="I13" s="126"/>
+      <c r="I13" s="143"/>
       <c r="J13" s="21"/>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:12" x14ac:dyDescent="0.55000000000000004">
       <c r="A14" s="19"/>
+      <c r="D14" s="146"/>
       <c r="J14" s="21"/>
     </row>
-    <row r="15" spans="1:10" ht="18.350000000000001" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:12" ht="18.399999999999999" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A15" s="19"/>
-      <c r="B15" s="127" t="s">
+      <c r="B15" s="124" t="s">
         <v>57</v>
       </c>
-      <c r="C15" s="128"/>
-      <c r="D15" s="22"/>
-      <c r="E15" s="133" t="s">
+      <c r="C15" s="125"/>
+      <c r="D15" s="144"/>
+      <c r="E15" s="130" t="s">
         <v>57</v>
       </c>
-      <c r="F15" s="133"/>
-      <c r="H15" s="133" t="s">
+      <c r="F15" s="130"/>
+      <c r="H15" s="130" t="s">
         <v>57</v>
       </c>
-      <c r="I15" s="133"/>
+      <c r="I15" s="130"/>
       <c r="J15" s="21"/>
     </row>
-    <row r="16" spans="1:10" ht="17.7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:12" ht="17.75" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A16" s="19"/>
-      <c r="B16" s="129"/>
-      <c r="C16" s="130"/>
-      <c r="D16" s="22"/>
-      <c r="E16" s="133"/>
-      <c r="F16" s="133"/>
-      <c r="H16" s="133"/>
-      <c r="I16" s="133"/>
+      <c r="B16" s="126"/>
+      <c r="C16" s="127"/>
+      <c r="D16" s="144"/>
+      <c r="E16" s="130"/>
+      <c r="F16" s="130"/>
+      <c r="H16" s="130"/>
+      <c r="I16" s="130"/>
       <c r="J16" s="21"/>
     </row>
-    <row r="17" spans="1:10" ht="18.350000000000001" x14ac:dyDescent="0.4">
+    <row r="17" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A17" s="19"/>
-      <c r="B17" s="129"/>
-      <c r="C17" s="130"/>
-      <c r="D17" s="22"/>
-      <c r="E17" s="133"/>
-      <c r="F17" s="133"/>
-      <c r="H17" s="133"/>
-      <c r="I17" s="133"/>
+      <c r="B17" s="126"/>
+      <c r="C17" s="127"/>
+      <c r="D17" s="144"/>
+      <c r="E17" s="130"/>
+      <c r="F17" s="130"/>
+      <c r="H17" s="130"/>
+      <c r="I17" s="130"/>
       <c r="J17" s="21"/>
     </row>
-    <row r="18" spans="1:10" ht="18.350000000000001" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="18" spans="1:10" ht="18.399999999999999" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A18" s="19"/>
-      <c r="B18" s="129"/>
-      <c r="C18" s="130"/>
-      <c r="D18" s="22"/>
-      <c r="E18" s="133"/>
-      <c r="F18" s="133"/>
-      <c r="H18" s="133"/>
-      <c r="I18" s="133"/>
+      <c r="B18" s="126"/>
+      <c r="C18" s="127"/>
+      <c r="D18" s="144"/>
+      <c r="E18" s="130"/>
+      <c r="F18" s="130"/>
+      <c r="H18" s="130"/>
+      <c r="I18" s="130"/>
       <c r="J18" s="21"/>
     </row>
-    <row r="19" spans="1:10" ht="17.7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="19" spans="1:10" ht="17.75" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A19" s="19"/>
-      <c r="B19" s="129"/>
-      <c r="C19" s="130"/>
-      <c r="D19" s="22"/>
-      <c r="E19" s="133"/>
-      <c r="F19" s="133"/>
-      <c r="H19" s="133"/>
-      <c r="I19" s="133"/>
+      <c r="B19" s="126"/>
+      <c r="C19" s="127"/>
+      <c r="D19" s="144"/>
+      <c r="E19" s="130"/>
+      <c r="F19" s="130"/>
+      <c r="H19" s="130"/>
+      <c r="I19" s="130"/>
       <c r="J19" s="21"/>
     </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.4">
+    <row r="20" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A20" s="19"/>
-      <c r="B20" s="129"/>
-      <c r="C20" s="130"/>
-      <c r="D20" s="23"/>
-      <c r="E20" s="133"/>
-      <c r="F20" s="133"/>
-      <c r="G20" s="24" t="s">
+      <c r="B20" s="126"/>
+      <c r="C20" s="127"/>
+      <c r="D20" s="145"/>
+      <c r="E20" s="130"/>
+      <c r="F20" s="130"/>
+      <c r="G20" s="22" t="s">
         <v>58</v>
       </c>
-      <c r="H20" s="133"/>
-      <c r="I20" s="133"/>
+      <c r="H20" s="130"/>
+      <c r="I20" s="130"/>
       <c r="J20" s="21"/>
     </row>
-    <row r="21" spans="1:10" ht="18.350000000000001" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="21" spans="1:10" ht="18.399999999999999" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A21" s="19"/>
-      <c r="B21" s="129"/>
-      <c r="C21" s="130"/>
-      <c r="D21" s="23"/>
-      <c r="E21" s="133"/>
-      <c r="F21" s="133"/>
-      <c r="G21" s="24"/>
-      <c r="H21" s="133"/>
-      <c r="I21" s="133"/>
+      <c r="B21" s="126"/>
+      <c r="C21" s="127"/>
+      <c r="D21" s="145"/>
+      <c r="E21" s="130"/>
+      <c r="F21" s="130"/>
+      <c r="G21" s="22"/>
+      <c r="H21" s="130"/>
+      <c r="I21" s="130"/>
       <c r="J21" s="21"/>
     </row>
-    <row r="22" spans="1:10" ht="17.7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="22" spans="1:10" ht="17.75" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A22" s="19"/>
-      <c r="B22" s="129"/>
-      <c r="C22" s="130"/>
-      <c r="D22" s="23"/>
-      <c r="E22" s="133"/>
-      <c r="F22" s="133"/>
-      <c r="G22" s="24"/>
-      <c r="H22" s="133"/>
-      <c r="I22" s="133"/>
+      <c r="B22" s="126"/>
+      <c r="C22" s="127"/>
+      <c r="D22" s="145"/>
+      <c r="E22" s="130"/>
+      <c r="F22" s="130"/>
+      <c r="G22" s="22"/>
+      <c r="H22" s="130"/>
+      <c r="I22" s="130"/>
       <c r="J22" s="21"/>
     </row>
-    <row r="23" spans="1:10" x14ac:dyDescent="0.4">
+    <row r="23" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A23" s="19"/>
-      <c r="B23" s="131"/>
-      <c r="C23" s="132"/>
-      <c r="D23" s="23"/>
-      <c r="E23" s="133"/>
-      <c r="F23" s="133"/>
-      <c r="G23" s="24"/>
-      <c r="H23" s="133"/>
-      <c r="I23" s="133"/>
+      <c r="B23" s="128"/>
+      <c r="C23" s="129"/>
+      <c r="D23" s="145"/>
+      <c r="E23" s="130"/>
+      <c r="F23" s="130"/>
+      <c r="G23" s="22"/>
+      <c r="H23" s="130"/>
+      <c r="I23" s="130"/>
       <c r="J23" s="21"/>
     </row>
-    <row r="24" spans="1:10" ht="18.350000000000001" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="24" spans="1:10" ht="18.399999999999999" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A24" s="19"/>
-      <c r="B24" s="124" t="s">
+      <c r="B24" s="141" t="s">
         <v>63</v>
       </c>
-      <c r="C24" s="125"/>
-      <c r="D24" s="23"/>
-      <c r="E24" s="126" t="s">
+      <c r="C24" s="142"/>
+      <c r="D24" s="145"/>
+      <c r="E24" s="143" t="s">
         <v>63</v>
       </c>
-      <c r="F24" s="126"/>
-      <c r="G24" s="24"/>
-      <c r="H24" s="126" t="s">
+      <c r="F24" s="143"/>
+      <c r="G24" s="22"/>
+      <c r="H24" s="143" t="s">
         <v>64</v>
       </c>
-      <c r="I24" s="126"/>
+      <c r="I24" s="143"/>
       <c r="J24" s="21"/>
     </row>
-    <row r="25" spans="1:10" x14ac:dyDescent="0.4">
+    <row r="25" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A25" s="19"/>
-      <c r="B25" s="25"/>
-      <c r="C25" s="25"/>
-      <c r="D25" s="25"/>
-      <c r="E25" s="25"/>
-      <c r="F25" s="25"/>
-      <c r="G25" s="26" t="s">
+      <c r="B25" s="23"/>
+      <c r="C25" s="23"/>
+      <c r="D25" s="145"/>
+      <c r="E25" s="23"/>
+      <c r="F25" s="23"/>
+      <c r="G25" s="24" t="s">
         <v>58</v>
       </c>
-      <c r="H25" s="25"/>
-      <c r="I25" s="25"/>
+      <c r="H25" s="23"/>
+      <c r="I25" s="23"/>
       <c r="J25" s="21"/>
     </row>
-    <row r="26" spans="1:10" ht="18.350000000000001" x14ac:dyDescent="0.4">
+    <row r="26" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A26" s="19"/>
-      <c r="B26" s="127" t="s">
+      <c r="B26" s="124" t="s">
         <v>57</v>
       </c>
-      <c r="C26" s="128"/>
-      <c r="D26" s="22"/>
-      <c r="E26" s="133" t="s">
+      <c r="C26" s="125"/>
+      <c r="D26" s="144"/>
+      <c r="E26" s="130" t="s">
         <v>57</v>
       </c>
-      <c r="F26" s="133"/>
-      <c r="H26" s="133" t="s">
+      <c r="F26" s="130"/>
+      <c r="H26" s="130" t="s">
         <v>57</v>
       </c>
-      <c r="I26" s="133"/>
+      <c r="I26" s="130"/>
       <c r="J26" s="21"/>
     </row>
-    <row r="27" spans="1:10" ht="18.350000000000001" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="27" spans="1:10" ht="18.399999999999999" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A27" s="19"/>
-      <c r="B27" s="129"/>
-      <c r="C27" s="130"/>
-      <c r="D27" s="22"/>
-      <c r="E27" s="133"/>
-      <c r="F27" s="133"/>
-      <c r="H27" s="133"/>
-      <c r="I27" s="133"/>
+      <c r="B27" s="126"/>
+      <c r="C27" s="127"/>
+      <c r="D27" s="144"/>
+      <c r="E27" s="130"/>
+      <c r="F27" s="130"/>
+      <c r="H27" s="130"/>
+      <c r="I27" s="130"/>
       <c r="J27" s="21"/>
     </row>
-    <row r="28" spans="1:10" ht="17.7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="28" spans="1:10" ht="17.75" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A28" s="19"/>
-      <c r="B28" s="129"/>
-      <c r="C28" s="130"/>
-      <c r="D28" s="22"/>
-      <c r="E28" s="133"/>
-      <c r="F28" s="133"/>
-      <c r="H28" s="133"/>
-      <c r="I28" s="133"/>
+      <c r="B28" s="126"/>
+      <c r="C28" s="127"/>
+      <c r="D28" s="144"/>
+      <c r="E28" s="130"/>
+      <c r="F28" s="130"/>
+      <c r="H28" s="130"/>
+      <c r="I28" s="130"/>
       <c r="J28" s="21"/>
     </row>
-    <row r="29" spans="1:10" ht="18.350000000000001" x14ac:dyDescent="0.4">
+    <row r="29" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A29" s="19"/>
-      <c r="B29" s="129"/>
-      <c r="C29" s="130"/>
-      <c r="D29" s="22"/>
-      <c r="E29" s="133"/>
-      <c r="F29" s="133"/>
-      <c r="H29" s="133"/>
-      <c r="I29" s="133"/>
+      <c r="B29" s="126"/>
+      <c r="C29" s="127"/>
+      <c r="D29" s="144"/>
+      <c r="E29" s="130"/>
+      <c r="F29" s="130"/>
+      <c r="H29" s="130"/>
+      <c r="I29" s="130"/>
       <c r="J29" s="21"/>
     </row>
-    <row r="30" spans="1:10" ht="18.350000000000001" x14ac:dyDescent="0.4">
+    <row r="30" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A30" s="19"/>
-      <c r="B30" s="129"/>
-      <c r="C30" s="130"/>
-      <c r="D30" s="22"/>
-      <c r="E30" s="133"/>
-      <c r="F30" s="133"/>
-      <c r="H30" s="133"/>
-      <c r="I30" s="133"/>
+      <c r="B30" s="126"/>
+      <c r="C30" s="127"/>
+      <c r="D30" s="144"/>
+      <c r="E30" s="130"/>
+      <c r="F30" s="130"/>
+      <c r="H30" s="130"/>
+      <c r="I30" s="130"/>
       <c r="J30" s="21"/>
     </row>
-    <row r="31" spans="1:10" x14ac:dyDescent="0.4">
+    <row r="31" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A31" s="19"/>
-      <c r="B31" s="129"/>
-      <c r="C31" s="130"/>
-      <c r="D31" s="23"/>
-      <c r="E31" s="133"/>
-      <c r="F31" s="133"/>
-      <c r="G31" s="24" t="s">
+      <c r="B31" s="126"/>
+      <c r="C31" s="127"/>
+      <c r="D31" s="145"/>
+      <c r="E31" s="130"/>
+      <c r="F31" s="130"/>
+      <c r="G31" s="22" t="s">
         <v>58</v>
       </c>
-      <c r="H31" s="133"/>
-      <c r="I31" s="133"/>
+      <c r="H31" s="130"/>
+      <c r="I31" s="130"/>
       <c r="J31" s="21"/>
     </row>
-    <row r="32" spans="1:10" x14ac:dyDescent="0.4">
+    <row r="32" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A32" s="19"/>
-      <c r="B32" s="129"/>
-      <c r="C32" s="130"/>
-      <c r="D32" s="23"/>
-      <c r="E32" s="133"/>
-      <c r="F32" s="133"/>
-      <c r="G32" s="24"/>
-      <c r="H32" s="133"/>
-      <c r="I32" s="133"/>
+      <c r="B32" s="126"/>
+      <c r="C32" s="127"/>
+      <c r="D32" s="145"/>
+      <c r="E32" s="130"/>
+      <c r="F32" s="130"/>
+      <c r="G32" s="22"/>
+      <c r="H32" s="130"/>
+      <c r="I32" s="130"/>
       <c r="J32" s="21"/>
     </row>
-    <row r="33" spans="1:10" x14ac:dyDescent="0.4">
+    <row r="33" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A33" s="19"/>
-      <c r="B33" s="129"/>
-      <c r="C33" s="130"/>
-      <c r="D33" s="23"/>
-      <c r="E33" s="133"/>
-      <c r="F33" s="133"/>
-      <c r="G33" s="24"/>
-      <c r="H33" s="133"/>
-      <c r="I33" s="133"/>
+      <c r="B33" s="126"/>
+      <c r="C33" s="127"/>
+      <c r="D33" s="145"/>
+      <c r="E33" s="130"/>
+      <c r="F33" s="130"/>
+      <c r="G33" s="22"/>
+      <c r="H33" s="130"/>
+      <c r="I33" s="130"/>
       <c r="J33" s="21"/>
     </row>
-    <row r="34" spans="1:10" x14ac:dyDescent="0.4">
+    <row r="34" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A34" s="19"/>
-      <c r="B34" s="131"/>
-      <c r="C34" s="132"/>
-      <c r="D34" s="23"/>
-      <c r="E34" s="133"/>
-      <c r="F34" s="133"/>
-      <c r="G34" s="24"/>
-      <c r="H34" s="133"/>
-      <c r="I34" s="133"/>
+      <c r="B34" s="128"/>
+      <c r="C34" s="129"/>
+      <c r="D34" s="145"/>
+      <c r="E34" s="130"/>
+      <c r="F34" s="130"/>
+      <c r="G34" s="22"/>
+      <c r="H34" s="130"/>
+      <c r="I34" s="130"/>
       <c r="J34" s="21"/>
     </row>
-    <row r="35" spans="1:10" x14ac:dyDescent="0.4">
+    <row r="35" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A35" s="19"/>
-      <c r="B35" s="124" t="s">
+      <c r="B35" s="141" t="s">
         <v>59</v>
       </c>
-      <c r="C35" s="125"/>
-      <c r="D35" s="23"/>
-      <c r="E35" s="126" t="s">
+      <c r="C35" s="142"/>
+      <c r="D35" s="145"/>
+      <c r="E35" s="143" t="s">
         <v>60</v>
       </c>
-      <c r="F35" s="126"/>
-      <c r="G35" s="24"/>
-      <c r="H35" s="126" t="s">
+      <c r="F35" s="143"/>
+      <c r="G35" s="22"/>
+      <c r="H35" s="143" t="s">
         <v>61</v>
       </c>
-      <c r="I35" s="126"/>
+      <c r="I35" s="143"/>
       <c r="J35" s="21"/>
     </row>
-    <row r="36" spans="1:10" x14ac:dyDescent="0.4">
-      <c r="A36" s="27"/>
-      <c r="B36" s="28"/>
-      <c r="C36" s="28"/>
-      <c r="D36" s="28"/>
-      <c r="E36" s="28"/>
-      <c r="F36" s="28"/>
-      <c r="G36" s="28"/>
-      <c r="H36" s="28"/>
-      <c r="I36" s="28"/>
-      <c r="J36" s="29"/>
+    <row r="36" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+      <c r="A36" s="25"/>
+      <c r="B36" s="26"/>
+      <c r="C36" s="26"/>
+      <c r="D36" s="26"/>
+      <c r="E36" s="26"/>
+      <c r="F36" s="26"/>
+      <c r="G36" s="26"/>
+      <c r="H36" s="26"/>
+      <c r="I36" s="26"/>
+      <c r="J36" s="27"/>
     </row>
   </sheetData>
   <mergeCells count="23">
-    <mergeCell ref="B4:C12"/>
-    <mergeCell ref="E4:F12"/>
-    <mergeCell ref="H4:I12"/>
-    <mergeCell ref="A1:J1"/>
-    <mergeCell ref="A2:B2"/>
-    <mergeCell ref="C2:E2"/>
-    <mergeCell ref="F2:G2"/>
-    <mergeCell ref="H2:J2"/>
-    <mergeCell ref="B13:C13"/>
-    <mergeCell ref="E13:F13"/>
-    <mergeCell ref="H13:I13"/>
-    <mergeCell ref="B15:C23"/>
-    <mergeCell ref="E15:F23"/>
-    <mergeCell ref="H15:I23"/>
     <mergeCell ref="B35:C35"/>
     <mergeCell ref="E35:F35"/>
     <mergeCell ref="H35:I35"/>
@@ -3552,6 +3530,20 @@
     <mergeCell ref="B26:C34"/>
     <mergeCell ref="E26:F34"/>
     <mergeCell ref="H26:I34"/>
+    <mergeCell ref="B13:C13"/>
+    <mergeCell ref="E13:F13"/>
+    <mergeCell ref="H13:I13"/>
+    <mergeCell ref="B15:C23"/>
+    <mergeCell ref="E15:F23"/>
+    <mergeCell ref="H15:I23"/>
+    <mergeCell ref="B4:C12"/>
+    <mergeCell ref="E4:F12"/>
+    <mergeCell ref="H4:I12"/>
+    <mergeCell ref="A1:J1"/>
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="C2:E2"/>
+    <mergeCell ref="F2:G2"/>
+    <mergeCell ref="H2:J2"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.31496062992125984" right="0.31496062992125984" top="0.51181102362204722" bottom="0.31496062992125984" header="0.51181102362204722" footer="0.51181102362204722"/>
@@ -3566,58 +3558,56 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F5845FA4-988D-4571-AC59-F62C504A990F}">
   <dimension ref="A1:L36"/>
-  <sheetFormatPr defaultColWidth="8.625" defaultRowHeight="17.7" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultColWidth="8.6328125" defaultRowHeight="17.5" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
-    <col min="1" max="1" width="2.625" style="1" customWidth="1"/>
-    <col min="2" max="3" width="12.625" style="1" customWidth="1"/>
-    <col min="4" max="4" width="2.625" style="1" customWidth="1"/>
-    <col min="5" max="6" width="12.625" style="1" customWidth="1"/>
-    <col min="7" max="7" width="2.625" style="1" customWidth="1"/>
-    <col min="8" max="9" width="12.625" style="1" customWidth="1"/>
-    <col min="10" max="10" width="2.625" style="1" customWidth="1"/>
-    <col min="11" max="16384" width="8.625" style="1"/>
+    <col min="1" max="1" width="2.6328125" style="1" customWidth="1"/>
+    <col min="2" max="3" width="12.6328125" style="1" customWidth="1"/>
+    <col min="4" max="4" width="2.6328125" style="1" customWidth="1"/>
+    <col min="5" max="6" width="12.6328125" style="1" customWidth="1"/>
+    <col min="7" max="7" width="2.6328125" style="1" customWidth="1"/>
+    <col min="8" max="9" width="12.6328125" style="1" customWidth="1"/>
+    <col min="10" max="10" width="2.6328125" style="1" customWidth="1"/>
+    <col min="11" max="16384" width="8.6328125" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="56.4" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A1" s="134" t="s">
+    <row r="1" spans="1:12" ht="56.4" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A1" s="131" t="s">
         <v>65</v>
       </c>
-      <c r="B1" s="135"/>
-      <c r="C1" s="135"/>
-      <c r="D1" s="135"/>
-      <c r="E1" s="135"/>
-      <c r="F1" s="135"/>
-      <c r="G1" s="135"/>
-      <c r="H1" s="135"/>
-      <c r="I1" s="135"/>
-      <c r="J1" s="136"/>
-    </row>
-    <row r="2" spans="1:12" ht="21.1" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A2" s="137" t="s">
+      <c r="B1" s="132"/>
+      <c r="C1" s="132"/>
+      <c r="D1" s="132"/>
+      <c r="E1" s="132"/>
+      <c r="F1" s="132"/>
+      <c r="G1" s="132"/>
+      <c r="H1" s="132"/>
+      <c r="I1" s="132"/>
+      <c r="J1" s="133"/>
+    </row>
+    <row r="2" spans="1:12" ht="21.15" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A2" s="134" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="138"/>
-      <c r="C2" s="139" t="s">
+      <c r="B2" s="135"/>
+      <c r="C2" s="136" t="s">
         <v>56</v>
       </c>
-      <c r="D2" s="140"/>
-      <c r="E2" s="141"/>
-      <c r="F2" s="142" t="s">
+      <c r="D2" s="137"/>
+      <c r="E2" s="138"/>
+      <c r="F2" s="139" t="s">
         <v>30</v>
       </c>
-      <c r="G2" s="143"/>
-      <c r="H2" s="139" t="s">
+      <c r="G2" s="140"/>
+      <c r="H2" s="136" t="s">
         <v>56</v>
       </c>
-      <c r="I2" s="140"/>
-      <c r="J2" s="141"/>
-      <c r="L2" s="144" t="inlineStr">
-        <is>
-          <t xml:space="preserve">วิธีเซฟเป็น PDF ให้ได้ครบทุกหน้า (หน้าเอกสาร + หน้ารูปภาพ)</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" spans="1:12" ht="18.350000000000001" x14ac:dyDescent="0.4">
+      <c r="I2" s="137"/>
+      <c r="J2" s="138"/>
+      <c r="L2" s="37" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12" x14ac:dyDescent="0.55000000000000004">
       <c r="A3" s="19"/>
       <c r="B3" s="20"/>
       <c r="C3" s="20"/>
@@ -3628,455 +3618,436 @@
       <c r="H3" s="20"/>
       <c r="I3" s="20"/>
       <c r="J3" s="21"/>
-      <c r="L3" s="145" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1. File (แฟ้ม) → Save As (บันทึกเป็น) → เลือกชนิดไฟล์ PDF</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" spans="1:12" ht="18.350000000000001" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="L3" s="38" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" ht="18.399999999999999" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A4" s="19"/>
-      <c r="B4" s="127" t="s">
+      <c r="B4" s="124" t="s">
         <v>57</v>
       </c>
-      <c r="C4" s="128"/>
-      <c r="D4" s="22"/>
-      <c r="E4" s="133" t="s">
+      <c r="C4" s="125"/>
+      <c r="D4" s="144"/>
+      <c r="E4" s="130" t="s">
         <v>57</v>
       </c>
-      <c r="F4" s="133"/>
-      <c r="H4" s="133" t="s">
+      <c r="F4" s="130"/>
+      <c r="H4" s="130" t="s">
         <v>57</v>
       </c>
-      <c r="I4" s="133"/>
+      <c r="I4" s="130"/>
       <c r="J4" s="21"/>
-      <c r="L4" s="145" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2. กดปุ่ม Options... (ตัวเลือก...) → เลือก Entire workbook (ทั้งเวิร์กบุ๊ก) → OK</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" spans="1:12" ht="18.350000000000001" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="L4" s="38" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" ht="18.399999999999999" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A5" s="19"/>
-      <c r="B5" s="129"/>
-      <c r="C5" s="130"/>
-      <c r="D5" s="22"/>
-      <c r="E5" s="133"/>
-      <c r="F5" s="133"/>
-      <c r="H5" s="133"/>
-      <c r="I5" s="133"/>
+      <c r="B5" s="126"/>
+      <c r="C5" s="127"/>
+      <c r="D5" s="144"/>
+      <c r="E5" s="130"/>
+      <c r="F5" s="130"/>
+      <c r="H5" s="130"/>
+      <c r="I5" s="130"/>
       <c r="J5" s="21"/>
-      <c r="L5" s="145" t="inlineStr">
-        <is>
-          <t xml:space="preserve">3. กด Save (บันทึก)  — ข้อความนี้อยู่นอกขอบเขตพิมพ์ ไม่ติดไปใน PDF</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" spans="1:10" ht="18.350000000000001" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="L5" s="38" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" ht="18.399999999999999" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A6" s="19"/>
-      <c r="B6" s="129"/>
-      <c r="C6" s="130"/>
-      <c r="D6" s="22"/>
-      <c r="E6" s="133"/>
-      <c r="F6" s="133"/>
-      <c r="H6" s="133"/>
-      <c r="I6" s="133"/>
+      <c r="B6" s="126"/>
+      <c r="C6" s="127"/>
+      <c r="D6" s="144"/>
+      <c r="E6" s="130"/>
+      <c r="F6" s="130"/>
+      <c r="H6" s="130"/>
+      <c r="I6" s="130"/>
       <c r="J6" s="21"/>
     </row>
-    <row r="7" spans="1:10" ht="18.350000000000001" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:12" ht="18.399999999999999" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A7" s="19"/>
-      <c r="B7" s="129"/>
-      <c r="C7" s="130"/>
-      <c r="D7" s="22"/>
-      <c r="E7" s="133"/>
-      <c r="F7" s="133"/>
-      <c r="H7" s="133"/>
-      <c r="I7" s="133"/>
+      <c r="B7" s="126"/>
+      <c r="C7" s="127"/>
+      <c r="D7" s="144"/>
+      <c r="E7" s="130"/>
+      <c r="F7" s="130"/>
+      <c r="H7" s="130"/>
+      <c r="I7" s="130"/>
       <c r="J7" s="21"/>
     </row>
-    <row r="8" spans="1:10" ht="18.350000000000001" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:12" ht="18.399999999999999" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A8" s="19"/>
-      <c r="B8" s="129"/>
-      <c r="C8" s="130"/>
-      <c r="D8" s="22"/>
-      <c r="E8" s="133"/>
-      <c r="F8" s="133"/>
-      <c r="H8" s="133"/>
-      <c r="I8" s="133"/>
+      <c r="B8" s="126"/>
+      <c r="C8" s="127"/>
+      <c r="D8" s="144"/>
+      <c r="E8" s="130"/>
+      <c r="F8" s="130"/>
+      <c r="H8" s="130"/>
+      <c r="I8" s="130"/>
       <c r="J8" s="21"/>
     </row>
-    <row r="9" spans="1:10" ht="17.7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:12" ht="17.75" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A9" s="19"/>
-      <c r="B9" s="129"/>
-      <c r="C9" s="130"/>
-      <c r="D9" s="23"/>
-      <c r="E9" s="133"/>
-      <c r="F9" s="133"/>
-      <c r="G9" s="24" t="s">
+      <c r="B9" s="126"/>
+      <c r="C9" s="127"/>
+      <c r="D9" s="145"/>
+      <c r="E9" s="130"/>
+      <c r="F9" s="130"/>
+      <c r="G9" s="22" t="s">
         <v>58</v>
       </c>
-      <c r="H9" s="133"/>
-      <c r="I9" s="133"/>
+      <c r="H9" s="130"/>
+      <c r="I9" s="130"/>
       <c r="J9" s="21"/>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:12" x14ac:dyDescent="0.55000000000000004">
       <c r="A10" s="19"/>
-      <c r="B10" s="129"/>
-      <c r="C10" s="130"/>
-      <c r="D10" s="23"/>
-      <c r="E10" s="133"/>
-      <c r="F10" s="133"/>
-      <c r="G10" s="24"/>
-      <c r="H10" s="133"/>
-      <c r="I10" s="133"/>
+      <c r="B10" s="126"/>
+      <c r="C10" s="127"/>
+      <c r="D10" s="145"/>
+      <c r="E10" s="130"/>
+      <c r="F10" s="130"/>
+      <c r="G10" s="22"/>
+      <c r="H10" s="130"/>
+      <c r="I10" s="130"/>
       <c r="J10" s="21"/>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:12" x14ac:dyDescent="0.55000000000000004">
       <c r="A11" s="19"/>
-      <c r="B11" s="129"/>
-      <c r="C11" s="130"/>
-      <c r="D11" s="23"/>
-      <c r="E11" s="133"/>
-      <c r="F11" s="133"/>
-      <c r="G11" s="24"/>
-      <c r="H11" s="133"/>
-      <c r="I11" s="133"/>
+      <c r="B11" s="126"/>
+      <c r="C11" s="127"/>
+      <c r="D11" s="145"/>
+      <c r="E11" s="130"/>
+      <c r="F11" s="130"/>
+      <c r="G11" s="22"/>
+      <c r="H11" s="130"/>
+      <c r="I11" s="130"/>
       <c r="J11" s="21"/>
     </row>
-    <row r="12" spans="1:10" ht="17.7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:12" ht="17.75" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A12" s="19"/>
-      <c r="B12" s="131"/>
-      <c r="C12" s="132"/>
-      <c r="D12" s="23"/>
-      <c r="E12" s="133"/>
-      <c r="F12" s="133"/>
-      <c r="G12" s="24"/>
-      <c r="H12" s="133"/>
-      <c r="I12" s="133"/>
+      <c r="B12" s="128"/>
+      <c r="C12" s="129"/>
+      <c r="D12" s="145"/>
+      <c r="E12" s="130"/>
+      <c r="F12" s="130"/>
+      <c r="G12" s="22"/>
+      <c r="H12" s="130"/>
+      <c r="I12" s="130"/>
       <c r="J12" s="21"/>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:12" x14ac:dyDescent="0.55000000000000004">
       <c r="A13" s="19"/>
-      <c r="B13" s="124" t="s">
+      <c r="B13" s="141" t="s">
         <v>71</v>
       </c>
-      <c r="C13" s="125"/>
-      <c r="D13" s="23"/>
-      <c r="E13" s="126" t="s">
+      <c r="C13" s="142"/>
+      <c r="D13" s="145"/>
+      <c r="E13" s="143" t="s">
         <v>63</v>
       </c>
-      <c r="F13" s="126"/>
-      <c r="G13" s="24"/>
-      <c r="H13" s="126" t="s">
+      <c r="F13" s="143"/>
+      <c r="G13" s="22"/>
+      <c r="H13" s="143" t="s">
         <v>63</v>
       </c>
-      <c r="I13" s="126"/>
+      <c r="I13" s="143"/>
       <c r="J13" s="21"/>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:12" x14ac:dyDescent="0.55000000000000004">
       <c r="A14" s="19"/>
+      <c r="D14" s="146"/>
       <c r="J14" s="21"/>
     </row>
-    <row r="15" spans="1:10" ht="18.350000000000001" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:12" ht="18.399999999999999" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A15" s="19"/>
-      <c r="B15" s="127" t="s">
+      <c r="B15" s="124" t="s">
         <v>57</v>
       </c>
-      <c r="C15" s="128"/>
-      <c r="D15" s="22"/>
-      <c r="E15" s="133" t="s">
+      <c r="C15" s="125"/>
+      <c r="D15" s="144"/>
+      <c r="E15" s="130" t="s">
         <v>57</v>
       </c>
-      <c r="F15" s="133"/>
-      <c r="H15" s="133" t="s">
+      <c r="F15" s="130"/>
+      <c r="H15" s="130" t="s">
         <v>57</v>
       </c>
-      <c r="I15" s="133"/>
+      <c r="I15" s="130"/>
       <c r="J15" s="21"/>
     </row>
-    <row r="16" spans="1:10" ht="17.7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:12" ht="17.75" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A16" s="19"/>
-      <c r="B16" s="129"/>
-      <c r="C16" s="130"/>
-      <c r="D16" s="22"/>
-      <c r="E16" s="133"/>
-      <c r="F16" s="133"/>
-      <c r="H16" s="133"/>
-      <c r="I16" s="133"/>
+      <c r="B16" s="126"/>
+      <c r="C16" s="127"/>
+      <c r="D16" s="144"/>
+      <c r="E16" s="130"/>
+      <c r="F16" s="130"/>
+      <c r="H16" s="130"/>
+      <c r="I16" s="130"/>
       <c r="J16" s="21"/>
     </row>
-    <row r="17" spans="1:10" ht="18.350000000000001" x14ac:dyDescent="0.4">
+    <row r="17" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A17" s="19"/>
-      <c r="B17" s="129"/>
-      <c r="C17" s="130"/>
-      <c r="D17" s="22"/>
-      <c r="E17" s="133"/>
-      <c r="F17" s="133"/>
-      <c r="H17" s="133"/>
-      <c r="I17" s="133"/>
+      <c r="B17" s="126"/>
+      <c r="C17" s="127"/>
+      <c r="D17" s="144"/>
+      <c r="E17" s="130"/>
+      <c r="F17" s="130"/>
+      <c r="H17" s="130"/>
+      <c r="I17" s="130"/>
       <c r="J17" s="21"/>
     </row>
-    <row r="18" spans="1:10" ht="18.350000000000001" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="18" spans="1:10" ht="18.399999999999999" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A18" s="19"/>
-      <c r="B18" s="129"/>
-      <c r="C18" s="130"/>
-      <c r="D18" s="22"/>
-      <c r="E18" s="133"/>
-      <c r="F18" s="133"/>
-      <c r="H18" s="133"/>
-      <c r="I18" s="133"/>
+      <c r="B18" s="126"/>
+      <c r="C18" s="127"/>
+      <c r="D18" s="144"/>
+      <c r="E18" s="130"/>
+      <c r="F18" s="130"/>
+      <c r="H18" s="130"/>
+      <c r="I18" s="130"/>
       <c r="J18" s="21"/>
     </row>
-    <row r="19" spans="1:10" ht="17.7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="19" spans="1:10" ht="17.75" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A19" s="19"/>
-      <c r="B19" s="129"/>
-      <c r="C19" s="130"/>
-      <c r="D19" s="22"/>
-      <c r="E19" s="133"/>
-      <c r="F19" s="133"/>
-      <c r="H19" s="133"/>
-      <c r="I19" s="133"/>
+      <c r="B19" s="126"/>
+      <c r="C19" s="127"/>
+      <c r="D19" s="144"/>
+      <c r="E19" s="130"/>
+      <c r="F19" s="130"/>
+      <c r="H19" s="130"/>
+      <c r="I19" s="130"/>
       <c r="J19" s="21"/>
     </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.4">
+    <row r="20" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A20" s="19"/>
-      <c r="B20" s="129"/>
-      <c r="C20" s="130"/>
-      <c r="D20" s="23"/>
-      <c r="E20" s="133"/>
-      <c r="F20" s="133"/>
-      <c r="G20" s="24" t="s">
+      <c r="B20" s="126"/>
+      <c r="C20" s="127"/>
+      <c r="D20" s="145"/>
+      <c r="E20" s="130"/>
+      <c r="F20" s="130"/>
+      <c r="G20" s="22" t="s">
         <v>58</v>
       </c>
-      <c r="H20" s="133"/>
-      <c r="I20" s="133"/>
+      <c r="H20" s="130"/>
+      <c r="I20" s="130"/>
       <c r="J20" s="21"/>
     </row>
-    <row r="21" spans="1:10" ht="18.350000000000001" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="21" spans="1:10" ht="18.399999999999999" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A21" s="19"/>
-      <c r="B21" s="129"/>
-      <c r="C21" s="130"/>
-      <c r="D21" s="23"/>
-      <c r="E21" s="133"/>
-      <c r="F21" s="133"/>
-      <c r="G21" s="24"/>
-      <c r="H21" s="133"/>
-      <c r="I21" s="133"/>
+      <c r="B21" s="126"/>
+      <c r="C21" s="127"/>
+      <c r="D21" s="145"/>
+      <c r="E21" s="130"/>
+      <c r="F21" s="130"/>
+      <c r="G21" s="22"/>
+      <c r="H21" s="130"/>
+      <c r="I21" s="130"/>
       <c r="J21" s="21"/>
     </row>
-    <row r="22" spans="1:10" ht="17.7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="22" spans="1:10" ht="17.75" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A22" s="19"/>
-      <c r="B22" s="129"/>
-      <c r="C22" s="130"/>
-      <c r="D22" s="23"/>
-      <c r="E22" s="133"/>
-      <c r="F22" s="133"/>
-      <c r="G22" s="24"/>
-      <c r="H22" s="133"/>
-      <c r="I22" s="133"/>
+      <c r="B22" s="126"/>
+      <c r="C22" s="127"/>
+      <c r="D22" s="145"/>
+      <c r="E22" s="130"/>
+      <c r="F22" s="130"/>
+      <c r="G22" s="22"/>
+      <c r="H22" s="130"/>
+      <c r="I22" s="130"/>
       <c r="J22" s="21"/>
     </row>
-    <row r="23" spans="1:10" x14ac:dyDescent="0.4">
+    <row r="23" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A23" s="19"/>
-      <c r="B23" s="131"/>
-      <c r="C23" s="132"/>
-      <c r="D23" s="23"/>
-      <c r="E23" s="133"/>
-      <c r="F23" s="133"/>
-      <c r="G23" s="24"/>
-      <c r="H23" s="133"/>
-      <c r="I23" s="133"/>
+      <c r="B23" s="128"/>
+      <c r="C23" s="129"/>
+      <c r="D23" s="145"/>
+      <c r="E23" s="130"/>
+      <c r="F23" s="130"/>
+      <c r="G23" s="22"/>
+      <c r="H23" s="130"/>
+      <c r="I23" s="130"/>
       <c r="J23" s="21"/>
     </row>
-    <row r="24" spans="1:10" ht="18.350000000000001" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="24" spans="1:10" ht="18.399999999999999" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A24" s="19"/>
-      <c r="B24" s="124" t="s">
+      <c r="B24" s="141" t="s">
         <v>63</v>
       </c>
-      <c r="C24" s="125"/>
-      <c r="D24" s="23"/>
-      <c r="E24" s="126" t="s">
+      <c r="C24" s="142"/>
+      <c r="D24" s="145"/>
+      <c r="E24" s="143" t="s">
         <v>63</v>
       </c>
-      <c r="F24" s="126"/>
-      <c r="G24" s="24"/>
-      <c r="H24" s="126" t="s">
+      <c r="F24" s="143"/>
+      <c r="G24" s="22"/>
+      <c r="H24" s="143" t="s">
         <v>64</v>
       </c>
-      <c r="I24" s="126"/>
+      <c r="I24" s="143"/>
       <c r="J24" s="21"/>
     </row>
-    <row r="25" spans="1:10" x14ac:dyDescent="0.4">
+    <row r="25" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A25" s="19"/>
-      <c r="B25" s="25"/>
-      <c r="C25" s="25"/>
-      <c r="D25" s="25"/>
-      <c r="E25" s="25"/>
-      <c r="F25" s="25"/>
-      <c r="G25" s="26" t="s">
+      <c r="B25" s="23"/>
+      <c r="C25" s="23"/>
+      <c r="D25" s="145"/>
+      <c r="E25" s="23"/>
+      <c r="F25" s="23"/>
+      <c r="G25" s="24" t="s">
         <v>58</v>
       </c>
-      <c r="H25" s="25"/>
-      <c r="I25" s="25"/>
+      <c r="H25" s="23"/>
+      <c r="I25" s="23"/>
       <c r="J25" s="21"/>
     </row>
-    <row r="26" spans="1:10" ht="18.350000000000001" x14ac:dyDescent="0.4">
+    <row r="26" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A26" s="19"/>
-      <c r="B26" s="127" t="s">
+      <c r="B26" s="124" t="s">
         <v>57</v>
       </c>
-      <c r="C26" s="128"/>
-      <c r="D26" s="22"/>
-      <c r="E26" s="133" t="s">
+      <c r="C26" s="125"/>
+      <c r="D26" s="144"/>
+      <c r="E26" s="130" t="s">
         <v>57</v>
       </c>
-      <c r="F26" s="133"/>
-      <c r="H26" s="133" t="s">
+      <c r="F26" s="130"/>
+      <c r="H26" s="130" t="s">
         <v>57</v>
       </c>
-      <c r="I26" s="133"/>
+      <c r="I26" s="130"/>
       <c r="J26" s="21"/>
     </row>
-    <row r="27" spans="1:10" ht="18.350000000000001" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="27" spans="1:10" ht="18.399999999999999" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A27" s="19"/>
-      <c r="B27" s="129"/>
-      <c r="C27" s="130"/>
-      <c r="D27" s="22"/>
-      <c r="E27" s="133"/>
-      <c r="F27" s="133"/>
-      <c r="H27" s="133"/>
-      <c r="I27" s="133"/>
+      <c r="B27" s="126"/>
+      <c r="C27" s="127"/>
+      <c r="D27" s="144"/>
+      <c r="E27" s="130"/>
+      <c r="F27" s="130"/>
+      <c r="H27" s="130"/>
+      <c r="I27" s="130"/>
       <c r="J27" s="21"/>
     </row>
-    <row r="28" spans="1:10" ht="17.7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="28" spans="1:10" ht="17.75" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A28" s="19"/>
-      <c r="B28" s="129"/>
-      <c r="C28" s="130"/>
-      <c r="D28" s="22"/>
-      <c r="E28" s="133"/>
-      <c r="F28" s="133"/>
-      <c r="H28" s="133"/>
-      <c r="I28" s="133"/>
+      <c r="B28" s="126"/>
+      <c r="C28" s="127"/>
+      <c r="D28" s="144"/>
+      <c r="E28" s="130"/>
+      <c r="F28" s="130"/>
+      <c r="H28" s="130"/>
+      <c r="I28" s="130"/>
       <c r="J28" s="21"/>
     </row>
-    <row r="29" spans="1:10" ht="18.350000000000001" x14ac:dyDescent="0.4">
+    <row r="29" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A29" s="19"/>
-      <c r="B29" s="129"/>
-      <c r="C29" s="130"/>
-      <c r="D29" s="22"/>
-      <c r="E29" s="133"/>
-      <c r="F29" s="133"/>
-      <c r="H29" s="133"/>
-      <c r="I29" s="133"/>
+      <c r="B29" s="126"/>
+      <c r="C29" s="127"/>
+      <c r="D29" s="144"/>
+      <c r="E29" s="130"/>
+      <c r="F29" s="130"/>
+      <c r="H29" s="130"/>
+      <c r="I29" s="130"/>
       <c r="J29" s="21"/>
     </row>
-    <row r="30" spans="1:10" ht="18.350000000000001" x14ac:dyDescent="0.4">
+    <row r="30" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A30" s="19"/>
-      <c r="B30" s="129"/>
-      <c r="C30" s="130"/>
-      <c r="D30" s="22"/>
-      <c r="E30" s="133"/>
-      <c r="F30" s="133"/>
-      <c r="H30" s="133"/>
-      <c r="I30" s="133"/>
+      <c r="B30" s="126"/>
+      <c r="C30" s="127"/>
+      <c r="D30" s="144"/>
+      <c r="E30" s="130"/>
+      <c r="F30" s="130"/>
+      <c r="H30" s="130"/>
+      <c r="I30" s="130"/>
       <c r="J30" s="21"/>
     </row>
-    <row r="31" spans="1:10" x14ac:dyDescent="0.4">
+    <row r="31" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A31" s="19"/>
-      <c r="B31" s="129"/>
-      <c r="C31" s="130"/>
-      <c r="D31" s="23"/>
-      <c r="E31" s="133"/>
-      <c r="F31" s="133"/>
-      <c r="G31" s="24" t="s">
+      <c r="B31" s="126"/>
+      <c r="C31" s="127"/>
+      <c r="D31" s="145"/>
+      <c r="E31" s="130"/>
+      <c r="F31" s="130"/>
+      <c r="G31" s="22" t="s">
         <v>58</v>
       </c>
-      <c r="H31" s="133"/>
-      <c r="I31" s="133"/>
+      <c r="H31" s="130"/>
+      <c r="I31" s="130"/>
       <c r="J31" s="21"/>
     </row>
-    <row r="32" spans="1:10" x14ac:dyDescent="0.4">
+    <row r="32" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A32" s="19"/>
-      <c r="B32" s="129"/>
-      <c r="C32" s="130"/>
-      <c r="D32" s="23"/>
-      <c r="E32" s="133"/>
-      <c r="F32" s="133"/>
-      <c r="G32" s="24"/>
-      <c r="H32" s="133"/>
-      <c r="I32" s="133"/>
+      <c r="B32" s="126"/>
+      <c r="C32" s="127"/>
+      <c r="D32" s="145"/>
+      <c r="E32" s="130"/>
+      <c r="F32" s="130"/>
+      <c r="G32" s="22"/>
+      <c r="H32" s="130"/>
+      <c r="I32" s="130"/>
       <c r="J32" s="21"/>
     </row>
-    <row r="33" spans="1:10" x14ac:dyDescent="0.4">
+    <row r="33" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A33" s="19"/>
-      <c r="B33" s="129"/>
-      <c r="C33" s="130"/>
-      <c r="D33" s="23"/>
-      <c r="E33" s="133"/>
-      <c r="F33" s="133"/>
-      <c r="G33" s="24"/>
-      <c r="H33" s="133"/>
-      <c r="I33" s="133"/>
+      <c r="B33" s="126"/>
+      <c r="C33" s="127"/>
+      <c r="D33" s="145"/>
+      <c r="E33" s="130"/>
+      <c r="F33" s="130"/>
+      <c r="G33" s="22"/>
+      <c r="H33" s="130"/>
+      <c r="I33" s="130"/>
       <c r="J33" s="21"/>
     </row>
-    <row r="34" spans="1:10" x14ac:dyDescent="0.4">
+    <row r="34" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A34" s="19"/>
-      <c r="B34" s="131"/>
-      <c r="C34" s="132"/>
-      <c r="D34" s="23"/>
-      <c r="E34" s="133"/>
-      <c r="F34" s="133"/>
-      <c r="G34" s="24"/>
-      <c r="H34" s="133"/>
-      <c r="I34" s="133"/>
+      <c r="B34" s="128"/>
+      <c r="C34" s="129"/>
+      <c r="D34" s="145"/>
+      <c r="E34" s="130"/>
+      <c r="F34" s="130"/>
+      <c r="G34" s="22"/>
+      <c r="H34" s="130"/>
+      <c r="I34" s="130"/>
       <c r="J34" s="21"/>
     </row>
-    <row r="35" spans="1:10" x14ac:dyDescent="0.4">
+    <row r="35" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A35" s="19"/>
-      <c r="B35" s="124" t="s">
+      <c r="B35" s="141" t="s">
         <v>59</v>
       </c>
-      <c r="C35" s="125"/>
-      <c r="D35" s="23"/>
-      <c r="E35" s="126" t="s">
+      <c r="C35" s="142"/>
+      <c r="D35" s="145"/>
+      <c r="E35" s="143" t="s">
         <v>60</v>
       </c>
-      <c r="F35" s="126"/>
-      <c r="G35" s="24"/>
-      <c r="H35" s="126" t="s">
+      <c r="F35" s="143"/>
+      <c r="G35" s="22"/>
+      <c r="H35" s="143" t="s">
         <v>61</v>
       </c>
-      <c r="I35" s="126"/>
+      <c r="I35" s="143"/>
       <c r="J35" s="21"/>
     </row>
-    <row r="36" spans="1:10" x14ac:dyDescent="0.4">
-      <c r="A36" s="27"/>
-      <c r="B36" s="28"/>
-      <c r="C36" s="28"/>
-      <c r="D36" s="28"/>
-      <c r="E36" s="28"/>
-      <c r="F36" s="28"/>
-      <c r="G36" s="28"/>
-      <c r="H36" s="28"/>
-      <c r="I36" s="28"/>
-      <c r="J36" s="29"/>
+    <row r="36" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+      <c r="A36" s="25"/>
+      <c r="B36" s="26"/>
+      <c r="C36" s="26"/>
+      <c r="D36" s="26"/>
+      <c r="E36" s="26"/>
+      <c r="F36" s="26"/>
+      <c r="G36" s="26"/>
+      <c r="H36" s="26"/>
+      <c r="I36" s="26"/>
+      <c r="J36" s="27"/>
     </row>
   </sheetData>
   <mergeCells count="23">
-    <mergeCell ref="B4:C12"/>
-    <mergeCell ref="E4:F12"/>
-    <mergeCell ref="H4:I12"/>
-    <mergeCell ref="A1:J1"/>
-    <mergeCell ref="A2:B2"/>
-    <mergeCell ref="C2:E2"/>
-    <mergeCell ref="F2:G2"/>
-    <mergeCell ref="H2:J2"/>
-    <mergeCell ref="B13:C13"/>
-    <mergeCell ref="E13:F13"/>
-    <mergeCell ref="H13:I13"/>
-    <mergeCell ref="B15:C23"/>
-    <mergeCell ref="E15:F23"/>
-    <mergeCell ref="H15:I23"/>
     <mergeCell ref="B35:C35"/>
     <mergeCell ref="E35:F35"/>
     <mergeCell ref="H35:I35"/>
@@ -4086,6 +4057,20 @@
     <mergeCell ref="B26:C34"/>
     <mergeCell ref="E26:F34"/>
     <mergeCell ref="H26:I34"/>
+    <mergeCell ref="B13:C13"/>
+    <mergeCell ref="E13:F13"/>
+    <mergeCell ref="H13:I13"/>
+    <mergeCell ref="B15:C23"/>
+    <mergeCell ref="E15:F23"/>
+    <mergeCell ref="H15:I23"/>
+    <mergeCell ref="B4:C12"/>
+    <mergeCell ref="E4:F12"/>
+    <mergeCell ref="H4:I12"/>
+    <mergeCell ref="A1:J1"/>
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="C2:E2"/>
+    <mergeCell ref="F2:G2"/>
+    <mergeCell ref="H2:J2"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.31496062992125984" right="0.31496062992125984" top="0.51181102362204722" bottom="0.31496062992125984" header="0.51181102362204722" footer="0.51181102362204722"/>
